--- a/research/traditional_assets/database/data/italy/italy_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_office_equipment_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1016304012860095</v>
+        <v>0.1014206883229231</v>
       </c>
       <c r="C2">
-        <v>953.9782989579475</v>
+        <v>946.0581777285962</v>
       </c>
       <c r="D2">
-        <v>895.4782989579475</v>
+        <v>897.2181777285962</v>
       </c>
       <c r="E2">
-        <v>-420.9</v>
+        <v>-411.24</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.66</v>
       </c>
       <c r="G2">
         <v>58.5</v>
@@ -1451,28 +1451,28 @@
         <v>119.775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.485898</v>
       </c>
       <c r="N2">
-        <v>119.775</v>
+        <v>119.289102</v>
       </c>
       <c r="O2">
-        <v>28.746</v>
+        <v>28.62938447999999</v>
       </c>
       <c r="P2">
-        <v>91.02899999999998</v>
+        <v>90.65971751999999</v>
       </c>
       <c r="Q2">
-        <v>132.129</v>
+        <v>131.75971752</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1016304012860095</v>
+        <v>0.1020589983059829</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431574</v>
+        <v>0.7744262878491454</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>246.502352345554</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1014206883229231</v>
+        <v>0.1012109753598367</v>
       </c>
       <c r="C3">
-        <v>946.0581777285962</v>
+        <v>938.1448306919352</v>
       </c>
       <c r="D3">
-        <v>897.2181777285962</v>
+        <v>898.9648306919353</v>
       </c>
       <c r="E3">
-        <v>-411.24</v>
+        <v>-401.58</v>
       </c>
       <c r="F3">
-        <v>9.66</v>
+        <v>19.32</v>
       </c>
       <c r="G3">
         <v>58.5</v>
@@ -1533,28 +1533,28 @@
         <v>119.775</v>
       </c>
       <c r="M3">
-        <v>0.485898</v>
+        <v>0.971796</v>
       </c>
       <c r="N3">
-        <v>119.289102</v>
+        <v>118.803204</v>
       </c>
       <c r="O3">
-        <v>28.62938447999999</v>
+        <v>28.51276896</v>
       </c>
       <c r="P3">
-        <v>90.65971751999999</v>
+        <v>90.29043503999998</v>
       </c>
       <c r="Q3">
-        <v>131.75971752</v>
+        <v>131.39043504</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1020589983059829</v>
+        <v>0.102496342203915</v>
       </c>
       <c r="T3">
-        <v>0.7744262878491454</v>
+        <v>0.7804464912226022</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>246.502352345554</v>
+        <v>123.251176172777</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1012109753598367</v>
+        <v>0.1010012623967503</v>
       </c>
       <c r="C4">
-        <v>938.1448306919352</v>
+        <v>930.2382974879647</v>
       </c>
       <c r="D4">
-        <v>898.9648306919353</v>
+        <v>900.7182974879647</v>
       </c>
       <c r="E4">
-        <v>-401.58</v>
+        <v>-391.92</v>
       </c>
       <c r="F4">
-        <v>19.32</v>
+        <v>28.98</v>
       </c>
       <c r="G4">
         <v>58.5</v>
@@ -1615,28 +1615,28 @@
         <v>119.775</v>
       </c>
       <c r="M4">
-        <v>0.971796</v>
+        <v>1.457694</v>
       </c>
       <c r="N4">
-        <v>118.803204</v>
+        <v>118.317306</v>
       </c>
       <c r="O4">
-        <v>28.51276896</v>
+        <v>28.39615343999999</v>
       </c>
       <c r="P4">
-        <v>90.29043503999998</v>
+        <v>89.92115255999998</v>
       </c>
       <c r="Q4">
-        <v>131.39043504</v>
+        <v>131.02115256</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.102496342203915</v>
+        <v>0.1029427035018044</v>
       </c>
       <c r="T4">
-        <v>0.7804464912226022</v>
+        <v>0.7865908225006668</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>123.251176172777</v>
+        <v>82.16745078185131</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1010012623967503</v>
+        <v>0.1007915494336638</v>
       </c>
       <c r="C5">
-        <v>930.2382974879647</v>
+        <v>922.3386180665665</v>
       </c>
       <c r="D5">
-        <v>900.7182974879647</v>
+        <v>902.4786180665665</v>
       </c>
       <c r="E5">
-        <v>-391.92</v>
+        <v>-382.26</v>
       </c>
       <c r="F5">
-        <v>28.98</v>
+        <v>38.64</v>
       </c>
       <c r="G5">
         <v>58.5</v>
@@ -1697,28 +1697,28 @@
         <v>119.775</v>
       </c>
       <c r="M5">
-        <v>1.457694</v>
+        <v>1.943592</v>
       </c>
       <c r="N5">
-        <v>118.317306</v>
+        <v>117.831408</v>
       </c>
       <c r="O5">
-        <v>28.39615343999999</v>
+        <v>28.27953792</v>
       </c>
       <c r="P5">
-        <v>89.92115255999998</v>
+        <v>89.55187007999999</v>
       </c>
       <c r="Q5">
-        <v>131.02115256</v>
+        <v>130.65187008</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1029427035018044</v>
+        <v>0.1033983639933998</v>
       </c>
       <c r="T5">
-        <v>0.7865908225006668</v>
+        <v>0.7928631606803574</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.16745078185131</v>
+        <v>61.62558808638849</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1007915494336638</v>
+        <v>0.1005818364705774</v>
       </c>
       <c r="C6">
-        <v>922.3386180665665</v>
+        <v>914.4458326905385</v>
       </c>
       <c r="D6">
-        <v>902.4786180665665</v>
+        <v>904.2458326905385</v>
       </c>
       <c r="E6">
-        <v>-382.26</v>
+        <v>-372.6</v>
       </c>
       <c r="F6">
-        <v>38.64</v>
+        <v>48.3</v>
       </c>
       <c r="G6">
         <v>58.5</v>
@@ -1779,28 +1779,28 @@
         <v>119.775</v>
       </c>
       <c r="M6">
-        <v>1.943592</v>
+        <v>2.42949</v>
       </c>
       <c r="N6">
-        <v>117.831408</v>
+        <v>117.34551</v>
       </c>
       <c r="O6">
-        <v>28.27953792</v>
+        <v>28.16292239999999</v>
       </c>
       <c r="P6">
-        <v>89.55187007999999</v>
+        <v>89.18258759999998</v>
       </c>
       <c r="Q6">
-        <v>130.65187008</v>
+        <v>130.2825876</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1033983639933998</v>
+        <v>0.1038636173374499</v>
       </c>
       <c r="T6">
-        <v>0.7928631606803574</v>
+        <v>0.7992675480848838</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.62558808638849</v>
+        <v>49.30047046911079</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1005818364705774</v>
+        <v>0.100372123507491</v>
       </c>
       <c r="C7">
-        <v>914.4458326905385</v>
+        <v>906.5599819386648</v>
       </c>
       <c r="D7">
-        <v>904.2458326905385</v>
+        <v>906.0199819386648</v>
       </c>
       <c r="E7">
-        <v>-372.6</v>
+        <v>-362.9399999999999</v>
       </c>
       <c r="F7">
-        <v>48.3</v>
+        <v>57.96000000000001</v>
       </c>
       <c r="G7">
         <v>58.5</v>
@@ -1861,28 +1861,28 @@
         <v>119.775</v>
       </c>
       <c r="M7">
-        <v>2.42949</v>
+        <v>2.915388</v>
       </c>
       <c r="N7">
-        <v>117.34551</v>
+        <v>116.859612</v>
       </c>
       <c r="O7">
-        <v>28.16292239999999</v>
+        <v>28.04630687999999</v>
       </c>
       <c r="P7">
-        <v>89.18258759999998</v>
+        <v>88.81330511999998</v>
       </c>
       <c r="Q7">
-        <v>130.2825876</v>
+        <v>129.91330512</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1038636173374499</v>
+        <v>0.1043387696888202</v>
       </c>
       <c r="T7">
-        <v>0.7992675480848838</v>
+        <v>0.8058081990512085</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.30047046911079</v>
+        <v>41.08372539092566</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.100372123507491</v>
+        <v>0.1001624105444046</v>
       </c>
       <c r="C8">
-        <v>906.5599819386648</v>
+        <v>898.6811067088213</v>
       </c>
       <c r="D8">
-        <v>906.0199819386648</v>
+        <v>907.8011067088213</v>
       </c>
       <c r="E8">
-        <v>-362.94</v>
+        <v>-353.28</v>
       </c>
       <c r="F8">
-        <v>57.96</v>
+        <v>67.61999999999999</v>
       </c>
       <c r="G8">
         <v>58.5</v>
@@ -1943,28 +1943,28 @@
         <v>119.775</v>
       </c>
       <c r="M8">
-        <v>2.915388</v>
+        <v>3.401285999999999</v>
       </c>
       <c r="N8">
-        <v>116.859612</v>
+        <v>116.373714</v>
       </c>
       <c r="O8">
-        <v>28.04630687999999</v>
+        <v>27.92969135999999</v>
       </c>
       <c r="P8">
-        <v>88.81330511999998</v>
+        <v>88.44402263999999</v>
       </c>
       <c r="Q8">
-        <v>129.91330512</v>
+        <v>129.54402264</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1043387696888202</v>
+        <v>0.1048241403703275</v>
       </c>
       <c r="T8">
-        <v>0.8058081990512085</v>
+        <v>0.8124895091780993</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.08372539092566</v>
+        <v>35.21462176365057</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1001624105444046</v>
+        <v>0.09995269758131817</v>
       </c>
       <c r="C9">
-        <v>898.6811067088213</v>
+        <v>890.8092482211175</v>
       </c>
       <c r="D9">
-        <v>907.8011067088213</v>
+        <v>909.5892482211175</v>
       </c>
       <c r="E9">
-        <v>-353.28</v>
+        <v>-343.62</v>
       </c>
       <c r="F9">
-        <v>67.62</v>
+        <v>77.28</v>
       </c>
       <c r="G9">
         <v>58.5</v>
@@ -2025,28 +2025,28 @@
         <v>119.775</v>
       </c>
       <c r="M9">
-        <v>3.401286</v>
+        <v>3.887184</v>
       </c>
       <c r="N9">
-        <v>116.373714</v>
+        <v>115.887816</v>
       </c>
       <c r="O9">
-        <v>27.92969135999999</v>
+        <v>27.81307583999999</v>
       </c>
       <c r="P9">
-        <v>88.44402263999999</v>
+        <v>88.07474015999998</v>
       </c>
       <c r="Q9">
-        <v>129.54402264</v>
+        <v>129.17474016</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1048241403703275</v>
+        <v>0.1053200625883893</v>
       </c>
       <c r="T9">
-        <v>0.8124895091780993</v>
+        <v>0.8193160651773138</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.21462176365056</v>
+        <v>30.81279404319424</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09995269758131817</v>
+        <v>0.09974298461823174</v>
       </c>
       <c r="C10">
-        <v>890.8092482211175</v>
+        <v>882.9444480210784</v>
       </c>
       <c r="D10">
-        <v>909.5892482211175</v>
+        <v>911.3844480210784</v>
       </c>
       <c r="E10">
-        <v>-343.62</v>
+        <v>-333.96</v>
       </c>
       <c r="F10">
-        <v>77.28</v>
+        <v>86.94</v>
       </c>
       <c r="G10">
         <v>58.5</v>
@@ -2107,28 +2107,28 @@
         <v>119.775</v>
       </c>
       <c r="M10">
-        <v>3.887184</v>
+        <v>4.373081999999999</v>
       </c>
       <c r="N10">
-        <v>115.887816</v>
+        <v>115.401918</v>
       </c>
       <c r="O10">
-        <v>27.81307583999999</v>
+        <v>27.69646031999999</v>
       </c>
       <c r="P10">
-        <v>88.07474015999998</v>
+        <v>87.70545767999999</v>
       </c>
       <c r="Q10">
-        <v>129.17474016</v>
+        <v>128.80545768</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1053200625883893</v>
+        <v>0.105826884195859</v>
       </c>
       <c r="T10">
-        <v>0.8193160651773138</v>
+        <v>0.8262926553743134</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.81279404319424</v>
+        <v>27.38915026061711</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09974298461823174</v>
+        <v>0.09953327165514531</v>
       </c>
       <c r="C11">
-        <v>882.9444480210784</v>
+        <v>875.0867479828596</v>
       </c>
       <c r="D11">
-        <v>911.3844480210784</v>
+        <v>913.1867479828596</v>
       </c>
       <c r="E11">
-        <v>-333.96</v>
+        <v>-324.3</v>
       </c>
       <c r="F11">
-        <v>86.94</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G11">
         <v>58.5</v>
@@ -2189,28 +2189,28 @@
         <v>119.775</v>
       </c>
       <c r="M11">
-        <v>4.373081999999999</v>
+        <v>4.85898</v>
       </c>
       <c r="N11">
-        <v>115.401918</v>
+        <v>114.91602</v>
       </c>
       <c r="O11">
-        <v>27.69646031999999</v>
+        <v>27.57984479999999</v>
       </c>
       <c r="P11">
-        <v>87.70545767999999</v>
+        <v>87.33617519999999</v>
       </c>
       <c r="Q11">
-        <v>128.80545768</v>
+        <v>128.4361752</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.105826884195859</v>
+        <v>0.106344968505717</v>
       </c>
       <c r="T11">
-        <v>0.8262926553743134</v>
+        <v>0.8334242809090241</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.38915026061711</v>
+        <v>24.6502352345554</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09953327165514531</v>
+        <v>0.09932355869205889</v>
       </c>
       <c r="C12">
-        <v>875.0867479828596</v>
+        <v>867.2361903125056</v>
       </c>
       <c r="D12">
-        <v>913.1867479828596</v>
+        <v>914.9961903125056</v>
       </c>
       <c r="E12">
-        <v>-324.3</v>
+        <v>-314.64</v>
       </c>
       <c r="F12">
-        <v>96.60000000000001</v>
+        <v>106.26</v>
       </c>
       <c r="G12">
         <v>58.5</v>
@@ -2271,28 +2271,28 @@
         <v>119.775</v>
       </c>
       <c r="M12">
-        <v>4.85898</v>
+        <v>5.344878</v>
       </c>
       <c r="N12">
-        <v>114.91602</v>
+        <v>114.430122</v>
       </c>
       <c r="O12">
-        <v>27.57984479999999</v>
+        <v>27.46322928</v>
       </c>
       <c r="P12">
-        <v>87.33617519999999</v>
+        <v>86.96689271999999</v>
       </c>
       <c r="Q12">
-        <v>128.4361752</v>
+        <v>128.06689272</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.106344968505717</v>
+        <v>0.1068746951596167</v>
       </c>
       <c r="T12">
-        <v>0.8334242809090241</v>
+        <v>0.8407161676917058</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.6502352345554</v>
+        <v>22.40930475868673</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09932355869205889</v>
+        <v>0.09911384572897246</v>
       </c>
       <c r="C13">
-        <v>867.2361903125056</v>
+        <v>859.3928175512424</v>
       </c>
       <c r="D13">
-        <v>914.9961903125056</v>
+        <v>916.8128175512423</v>
       </c>
       <c r="E13">
-        <v>-314.64</v>
+        <v>-304.98</v>
       </c>
       <c r="F13">
-        <v>106.26</v>
+        <v>115.92</v>
       </c>
       <c r="G13">
         <v>58.5</v>
@@ -2353,28 +2353,28 @@
         <v>119.775</v>
       </c>
       <c r="M13">
-        <v>5.344878</v>
+        <v>5.830776</v>
       </c>
       <c r="N13">
-        <v>114.430122</v>
+        <v>113.944224</v>
       </c>
       <c r="O13">
-        <v>27.46322928</v>
+        <v>27.34661375999999</v>
       </c>
       <c r="P13">
-        <v>86.96689271999999</v>
+        <v>86.59761023999998</v>
       </c>
       <c r="Q13">
-        <v>128.06689272</v>
+        <v>127.69761024</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1068746951596167</v>
+        <v>0.1074164610556505</v>
       </c>
       <c r="T13">
-        <v>0.8407161676917058</v>
+        <v>0.8481737791739936</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.40930475868673</v>
+        <v>20.54186269546283</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09911384572897246</v>
+        <v>0.09890413276588604</v>
       </c>
       <c r="C14">
-        <v>859.3928175512424</v>
+        <v>851.5566725788127</v>
       </c>
       <c r="D14">
-        <v>916.8128175512423</v>
+        <v>918.6366725788127</v>
       </c>
       <c r="E14">
-        <v>-304.98</v>
+        <v>-295.32</v>
       </c>
       <c r="F14">
-        <v>115.92</v>
+        <v>125.58</v>
       </c>
       <c r="G14">
         <v>58.5</v>
@@ -2435,28 +2435,28 @@
         <v>119.775</v>
       </c>
       <c r="M14">
-        <v>5.830776</v>
+        <v>6.316674</v>
       </c>
       <c r="N14">
-        <v>113.944224</v>
+        <v>113.458326</v>
       </c>
       <c r="O14">
-        <v>27.34661375999999</v>
+        <v>27.22999823999999</v>
       </c>
       <c r="P14">
-        <v>86.59761023999998</v>
+        <v>86.22832775999998</v>
       </c>
       <c r="Q14">
-        <v>127.69761024</v>
+        <v>127.32832776</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1074164610556505</v>
+        <v>0.1079706813400989</v>
       </c>
       <c r="T14">
-        <v>0.8481737791739936</v>
+        <v>0.8558028300007022</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.54186269546283</v>
+        <v>18.96171941119646</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09890413276588604</v>
+        <v>0.09869441980279961</v>
       </c>
       <c r="C15">
-        <v>851.5566725788127</v>
+        <v>843.7277986168497</v>
       </c>
       <c r="D15">
-        <v>918.6366725788127</v>
+        <v>920.4677986168497</v>
       </c>
       <c r="E15">
-        <v>-295.32</v>
+        <v>-285.66</v>
       </c>
       <c r="F15">
-        <v>125.58</v>
+        <v>135.24</v>
       </c>
       <c r="G15">
         <v>58.5</v>
@@ -2517,28 +2517,28 @@
         <v>119.775</v>
       </c>
       <c r="M15">
-        <v>6.316674</v>
+        <v>6.802572000000001</v>
       </c>
       <c r="N15">
-        <v>113.458326</v>
+        <v>112.972428</v>
       </c>
       <c r="O15">
-        <v>27.22999823999999</v>
+        <v>27.11338271999999</v>
       </c>
       <c r="P15">
-        <v>86.22832775999998</v>
+        <v>85.85904527999999</v>
       </c>
       <c r="Q15">
-        <v>127.32832776</v>
+        <v>126.95904528</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1079706813400989</v>
+        <v>0.1085377904683716</v>
       </c>
       <c r="T15">
-        <v>0.8558028300007022</v>
+        <v>0.8636093006140783</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.96171941119646</v>
+        <v>17.60731088182528</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09869441980279961</v>
+        <v>0.09848470683971319</v>
       </c>
       <c r="C16">
-        <v>843.7277986168497</v>
+        <v>835.9062392322901</v>
       </c>
       <c r="D16">
-        <v>920.4677986168497</v>
+        <v>922.3062392322902</v>
       </c>
       <c r="E16">
-        <v>-285.66</v>
+        <v>-275.9999999999999</v>
       </c>
       <c r="F16">
-        <v>135.24</v>
+        <v>144.9</v>
       </c>
       <c r="G16">
         <v>58.5</v>
@@ -2599,28 +2599,28 @@
         <v>119.775</v>
       </c>
       <c r="M16">
-        <v>6.802572000000001</v>
+        <v>7.288470000000001</v>
       </c>
       <c r="N16">
-        <v>112.972428</v>
+        <v>112.48653</v>
       </c>
       <c r="O16">
-        <v>27.11338271999999</v>
+        <v>26.99676719999999</v>
       </c>
       <c r="P16">
-        <v>85.85904527999999</v>
+        <v>85.48976279999998</v>
       </c>
       <c r="Q16">
-        <v>126.95904528</v>
+        <v>126.5897628</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1085377904683716</v>
+        <v>0.1091182433408391</v>
       </c>
       <c r="T16">
-        <v>0.8636093006140783</v>
+        <v>0.8715994528889457</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.60731088182528</v>
+        <v>16.43349015637026</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09848470683971319</v>
+        <v>0.09827499387662676</v>
       </c>
       <c r="C17">
-        <v>835.9062392322902</v>
+        <v>828.0920383408313</v>
       </c>
       <c r="D17">
-        <v>922.3062392322902</v>
+        <v>924.1520383408314</v>
       </c>
       <c r="E17">
-        <v>-276</v>
+        <v>-266.34</v>
       </c>
       <c r="F17">
-        <v>144.9</v>
+        <v>154.56</v>
       </c>
       <c r="G17">
         <v>58.5</v>
@@ -2681,28 +2681,28 @@
         <v>119.775</v>
       </c>
       <c r="M17">
-        <v>7.28847</v>
+        <v>7.774368</v>
       </c>
       <c r="N17">
-        <v>112.48653</v>
+        <v>112.000632</v>
       </c>
       <c r="O17">
-        <v>26.99676719999999</v>
+        <v>26.88015167999999</v>
       </c>
       <c r="P17">
-        <v>85.48976279999998</v>
+        <v>85.12048031999998</v>
       </c>
       <c r="Q17">
-        <v>126.5897628</v>
+        <v>126.22048032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1091182433408391</v>
+        <v>0.1097125165197938</v>
       </c>
       <c r="T17">
-        <v>0.8715994528889456</v>
+        <v>0.8797798468846432</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.43349015637026</v>
+        <v>15.40639702159712</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09827499387662676</v>
+        <v>0.09806528091354036</v>
       </c>
       <c r="C18">
-        <v>828.0920383408313</v>
+        <v>820.2852402104269</v>
       </c>
       <c r="D18">
-        <v>924.1520383408314</v>
+        <v>926.0052402104269</v>
       </c>
       <c r="E18">
-        <v>-266.34</v>
+        <v>-256.6799999999999</v>
       </c>
       <c r="F18">
-        <v>154.56</v>
+        <v>164.22</v>
       </c>
       <c r="G18">
         <v>58.5</v>
@@ -2763,28 +2763,28 @@
         <v>119.775</v>
       </c>
       <c r="M18">
-        <v>7.774368</v>
+        <v>8.260266</v>
       </c>
       <c r="N18">
-        <v>112.000632</v>
+        <v>111.514734</v>
       </c>
       <c r="O18">
-        <v>26.88015167999999</v>
+        <v>26.76353615999999</v>
       </c>
       <c r="P18">
-        <v>85.12048031999998</v>
+        <v>84.75119783999997</v>
       </c>
       <c r="Q18">
-        <v>126.22048032</v>
+        <v>125.85119784</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1097125165197938</v>
+        <v>0.110321109534386</v>
       </c>
       <c r="T18">
-        <v>0.8797798468846432</v>
+        <v>0.8881573588079478</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.40639702159712</v>
+        <v>14.50013837326788</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09806528091354036</v>
+        <v>0.09785556795045394</v>
       </c>
       <c r="C19">
-        <v>820.2852402104269</v>
+        <v>812.4858894648258</v>
       </c>
       <c r="D19">
-        <v>926.0052402104269</v>
+        <v>927.8658894648258</v>
       </c>
       <c r="E19">
-        <v>-256.6799999999999</v>
+        <v>-247.02</v>
       </c>
       <c r="F19">
-        <v>164.22</v>
+        <v>173.88</v>
       </c>
       <c r="G19">
         <v>58.5</v>
@@ -2845,28 +2845,28 @@
         <v>119.775</v>
       </c>
       <c r="M19">
-        <v>8.260266</v>
+        <v>8.746164</v>
       </c>
       <c r="N19">
-        <v>111.514734</v>
+        <v>111.028836</v>
       </c>
       <c r="O19">
-        <v>26.76353615999999</v>
+        <v>26.64692063999999</v>
       </c>
       <c r="P19">
-        <v>84.75119783999997</v>
+        <v>84.38191535999999</v>
       </c>
       <c r="Q19">
-        <v>125.85119784</v>
+        <v>125.48191536</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.110321109534386</v>
+        <v>0.1109445462810414</v>
       </c>
       <c r="T19">
-        <v>0.8881573588079478</v>
+        <v>0.8967392002903575</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.50013837326788</v>
+        <v>13.69457513030855</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09785556795045393</v>
+        <v>0.0976458549873675</v>
       </c>
       <c r="C20">
-        <v>812.4858894648261</v>
+        <v>804.6940310871549</v>
       </c>
       <c r="D20">
-        <v>927.8658894648261</v>
+        <v>929.7340310871549</v>
       </c>
       <c r="E20">
-        <v>-247.02</v>
+        <v>-237.36</v>
       </c>
       <c r="F20">
-        <v>173.88</v>
+        <v>183.54</v>
       </c>
       <c r="G20">
         <v>58.5</v>
@@ -2927,28 +2927,28 @@
         <v>119.775</v>
       </c>
       <c r="M20">
-        <v>8.746163999999998</v>
+        <v>9.232061999999999</v>
       </c>
       <c r="N20">
-        <v>111.028836</v>
+        <v>110.542938</v>
       </c>
       <c r="O20">
-        <v>26.64692063999999</v>
+        <v>26.53030511999999</v>
       </c>
       <c r="P20">
-        <v>84.38191535999999</v>
+        <v>84.01263287999998</v>
       </c>
       <c r="Q20">
-        <v>125.48191536</v>
+        <v>125.11263288</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1109445462810414</v>
+        <v>0.1115833765276142</v>
       </c>
       <c r="T20">
-        <v>0.8967392002903573</v>
+        <v>0.9055329390933202</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.69457513030856</v>
+        <v>12.97380801818705</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0976458549873675</v>
+        <v>0.09766414202428107</v>
       </c>
       <c r="C21">
-        <v>804.6940310871549</v>
+        <v>794.8708292140166</v>
       </c>
       <c r="D21">
-        <v>929.7340310871549</v>
+        <v>929.5708292140166</v>
       </c>
       <c r="E21">
-        <v>-237.36</v>
+        <v>-227.7</v>
       </c>
       <c r="F21">
-        <v>183.54</v>
+        <v>193.2</v>
       </c>
       <c r="G21">
         <v>58.5</v>
@@ -3009,45 +3009,45 @@
         <v>119.775</v>
       </c>
       <c r="M21">
-        <v>9.232061999999999</v>
+        <v>10.00776</v>
       </c>
       <c r="N21">
-        <v>110.542938</v>
+        <v>109.76724</v>
       </c>
       <c r="O21">
-        <v>26.53030511999999</v>
+        <v>26.34413759999999</v>
       </c>
       <c r="P21">
-        <v>84.01263287999998</v>
+        <v>83.42310239999998</v>
       </c>
       <c r="Q21">
-        <v>125.11263288</v>
+        <v>124.5231024</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1115833765276142</v>
+        <v>0.1122381775303513</v>
       </c>
       <c r="T21">
-        <v>0.9055329390933202</v>
+        <v>0.9145465213663573</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>12.97380801818705</v>
+        <v>11.96821266697043</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09766414202428107</v>
+        <v>0.09746582906119466</v>
       </c>
       <c r="C22">
-        <v>794.8708292140166</v>
+        <v>786.9837289199029</v>
       </c>
       <c r="D22">
-        <v>929.5708292140166</v>
+        <v>931.3437289199029</v>
       </c>
       <c r="E22">
-        <v>-227.7</v>
+        <v>-218.04</v>
       </c>
       <c r="F22">
-        <v>193.2</v>
+        <v>202.86</v>
       </c>
       <c r="G22">
         <v>58.5</v>
@@ -3091,28 +3091,28 @@
         <v>119.775</v>
       </c>
       <c r="M22">
-        <v>10.00776</v>
+        <v>10.508148</v>
       </c>
       <c r="N22">
-        <v>109.76724</v>
+        <v>109.266852</v>
       </c>
       <c r="O22">
-        <v>26.34413759999999</v>
+        <v>26.22404447999999</v>
       </c>
       <c r="P22">
-        <v>83.42310239999998</v>
+        <v>83.04280751999998</v>
       </c>
       <c r="Q22">
-        <v>124.5231024</v>
+        <v>124.14280752</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1122381775303513</v>
+        <v>0.1129095557736641</v>
       </c>
       <c r="T22">
-        <v>0.9145465213663573</v>
+        <v>0.9237882955956738</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.96821266697043</v>
+        <v>11.39829777806707</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09746582906119466</v>
+        <v>0.09726751609810824</v>
       </c>
       <c r="C23">
-        <v>786.9837289199029</v>
+        <v>779.1034041816881</v>
       </c>
       <c r="D23">
-        <v>931.3437289199029</v>
+        <v>933.1234041816881</v>
       </c>
       <c r="E23">
-        <v>-218.04</v>
+        <v>-208.38</v>
       </c>
       <c r="F23">
-        <v>202.86</v>
+        <v>212.52</v>
       </c>
       <c r="G23">
         <v>58.5</v>
@@ -3173,28 +3173,28 @@
         <v>119.775</v>
       </c>
       <c r="M23">
-        <v>10.508148</v>
+        <v>11.008536</v>
       </c>
       <c r="N23">
-        <v>109.266852</v>
+        <v>108.766464</v>
       </c>
       <c r="O23">
-        <v>26.22404447999999</v>
+        <v>26.10395136</v>
       </c>
       <c r="P23">
-        <v>83.04280751999998</v>
+        <v>82.66251263999999</v>
       </c>
       <c r="Q23">
-        <v>124.14280752</v>
+        <v>123.76251264</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1129095557736641</v>
+        <v>0.1135981488437285</v>
       </c>
       <c r="T23">
-        <v>0.9237882955956738</v>
+        <v>0.9332670383949727</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.39829777806708</v>
+        <v>10.88019333360948</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09726751609810824</v>
+        <v>0.09706920313502182</v>
       </c>
       <c r="C24">
-        <v>779.1034041816881</v>
+        <v>771.2298939153216</v>
       </c>
       <c r="D24">
-        <v>933.1234041816881</v>
+        <v>934.9098939153215</v>
       </c>
       <c r="E24">
-        <v>-208.38</v>
+        <v>-198.72</v>
       </c>
       <c r="F24">
-        <v>212.52</v>
+        <v>222.18</v>
       </c>
       <c r="G24">
         <v>58.5</v>
@@ -3255,28 +3255,28 @@
         <v>119.775</v>
       </c>
       <c r="M24">
-        <v>11.008536</v>
+        <v>11.508924</v>
       </c>
       <c r="N24">
-        <v>108.766464</v>
+        <v>108.266076</v>
       </c>
       <c r="O24">
-        <v>26.10395136</v>
+        <v>25.98385823999999</v>
       </c>
       <c r="P24">
-        <v>82.66251263999999</v>
+        <v>82.28221775999998</v>
       </c>
       <c r="Q24">
-        <v>123.76251264</v>
+        <v>123.38221776</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1135981488437285</v>
+        <v>0.1143046274480803</v>
       </c>
       <c r="T24">
-        <v>0.9332670383949727</v>
+        <v>0.9429919823059418</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.88019333360948</v>
+        <v>10.4071414495395</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09706920313502182</v>
+        <v>0.09687089017193537</v>
       </c>
       <c r="C25">
-        <v>771.2298939153216</v>
+        <v>763.363237335347</v>
       </c>
       <c r="D25">
-        <v>934.9098939153215</v>
+        <v>936.703237335347</v>
       </c>
       <c r="E25">
-        <v>-198.72</v>
+        <v>-189.0599999999999</v>
       </c>
       <c r="F25">
-        <v>222.18</v>
+        <v>231.84</v>
       </c>
       <c r="G25">
         <v>58.5</v>
@@ -3337,28 +3337,28 @@
         <v>119.775</v>
       </c>
       <c r="M25">
-        <v>11.508924</v>
+        <v>12.009312</v>
       </c>
       <c r="N25">
-        <v>108.266076</v>
+        <v>107.765688</v>
       </c>
       <c r="O25">
-        <v>25.98385823999999</v>
+        <v>25.86376512</v>
       </c>
       <c r="P25">
-        <v>82.28221775999998</v>
+        <v>81.90192287999999</v>
       </c>
       <c r="Q25">
-        <v>123.38221776</v>
+        <v>123.00192288</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1143046274480803</v>
+        <v>0.1150296975946518</v>
       </c>
       <c r="T25">
-        <v>0.9429919823059418</v>
+        <v>0.9529728457935152</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.4071414495395</v>
+        <v>9.973510555808691</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09687089017193537</v>
+        <v>0.09699557720884897</v>
       </c>
       <c r="C26">
-        <v>763.363237335347</v>
+        <v>752.5748908868979</v>
       </c>
       <c r="D26">
-        <v>936.703237335347</v>
+        <v>935.5748908868979</v>
       </c>
       <c r="E26">
-        <v>-189.06</v>
+        <v>-179.4</v>
       </c>
       <c r="F26">
-        <v>231.84</v>
+        <v>241.5</v>
       </c>
       <c r="G26">
         <v>58.5</v>
@@ -3419,45 +3419,45 @@
         <v>119.775</v>
       </c>
       <c r="M26">
-        <v>12.009312</v>
+        <v>12.92025</v>
       </c>
       <c r="N26">
-        <v>107.765688</v>
+        <v>106.85475</v>
       </c>
       <c r="O26">
-        <v>25.86376512</v>
+        <v>25.64513999999999</v>
       </c>
       <c r="P26">
-        <v>81.90192287999999</v>
+        <v>81.20960999999998</v>
       </c>
       <c r="Q26">
-        <v>123.00192288</v>
+        <v>122.30961</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1150296975946518</v>
+        <v>0.115774102945132</v>
       </c>
       <c r="T26">
-        <v>0.9529728457935152</v>
+        <v>0.9632198656407573</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.973510555808691</v>
+        <v>9.270331456434665</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09699557720884897</v>
+        <v>0.09681018424576253</v>
       </c>
       <c r="C27">
-        <v>752.5748908868979</v>
+        <v>744.5935769814201</v>
       </c>
       <c r="D27">
-        <v>935.5748908868979</v>
+        <v>937.2535769814201</v>
       </c>
       <c r="E27">
-        <v>-179.4</v>
+        <v>-169.74</v>
       </c>
       <c r="F27">
-        <v>241.5</v>
+        <v>251.16</v>
       </c>
       <c r="G27">
         <v>58.5</v>
@@ -3501,28 +3501,28 @@
         <v>119.775</v>
       </c>
       <c r="M27">
-        <v>12.92025</v>
+        <v>13.43706</v>
       </c>
       <c r="N27">
-        <v>106.85475</v>
+        <v>106.33794</v>
       </c>
       <c r="O27">
-        <v>25.64513999999999</v>
+        <v>25.52110559999999</v>
       </c>
       <c r="P27">
-        <v>81.20960999999998</v>
+        <v>80.81683439999998</v>
       </c>
       <c r="Q27">
-        <v>122.30961</v>
+        <v>121.9168344</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.115774102945132</v>
+        <v>0.1165386273591386</v>
       </c>
       <c r="T27">
-        <v>0.9632198656407573</v>
+        <v>0.9737438319703572</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.270331456434665</v>
+        <v>8.913780246571793</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09681018424576253</v>
+        <v>0.09662479128267612</v>
       </c>
       <c r="C28">
-        <v>744.5935769814201</v>
+        <v>736.6182979800126</v>
       </c>
       <c r="D28">
-        <v>937.2535769814201</v>
+        <v>938.9382979800126</v>
       </c>
       <c r="E28">
-        <v>-169.74</v>
+        <v>-160.08</v>
       </c>
       <c r="F28">
-        <v>251.16</v>
+        <v>260.82</v>
       </c>
       <c r="G28">
         <v>58.5</v>
@@ -3583,28 +3583,28 @@
         <v>119.775</v>
       </c>
       <c r="M28">
-        <v>13.43706</v>
+        <v>13.95387</v>
       </c>
       <c r="N28">
-        <v>106.33794</v>
+        <v>105.82113</v>
       </c>
       <c r="O28">
-        <v>25.52110559999999</v>
+        <v>25.3970712</v>
       </c>
       <c r="P28">
-        <v>80.81683439999998</v>
+        <v>80.42405879999998</v>
       </c>
       <c r="Q28">
-        <v>121.9168344</v>
+        <v>121.5240588</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1165386273591386</v>
+        <v>0.1173240976475015</v>
       </c>
       <c r="T28">
-        <v>0.9737438319703572</v>
+        <v>0.9845561261446039</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.913780246571793</v>
+        <v>8.583640237439504</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09662479128267612</v>
+        <v>0.0964393983195897</v>
       </c>
       <c r="C29">
-        <v>736.6182979800126</v>
+        <v>728.6490864846471</v>
       </c>
       <c r="D29">
-        <v>938.9382979800126</v>
+        <v>940.6290864846471</v>
       </c>
       <c r="E29">
-        <v>-160.08</v>
+        <v>-150.42</v>
       </c>
       <c r="F29">
-        <v>260.82</v>
+        <v>270.48</v>
       </c>
       <c r="G29">
         <v>58.5</v>
@@ -3665,28 +3665,28 @@
         <v>119.775</v>
       </c>
       <c r="M29">
-        <v>13.95387</v>
+        <v>14.47068</v>
       </c>
       <c r="N29">
-        <v>105.82113</v>
+        <v>105.30432</v>
       </c>
       <c r="O29">
-        <v>25.3970712</v>
+        <v>25.27303679999999</v>
       </c>
       <c r="P29">
-        <v>80.42405879999998</v>
+        <v>80.03128319999999</v>
       </c>
       <c r="Q29">
-        <v>121.5240588</v>
+        <v>121.1312832</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1173240976475015</v>
+        <v>0.1181313865549857</v>
       </c>
       <c r="T29">
-        <v>0.9845561261446039</v>
+        <v>0.9956687618236906</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.583640237439504</v>
+        <v>8.27708165753095</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0964393983195897</v>
+        <v>0.09625400535650327</v>
       </c>
       <c r="C30">
-        <v>728.6490864846471</v>
+        <v>720.6859753325496</v>
       </c>
       <c r="D30">
-        <v>940.6290864846471</v>
+        <v>942.3259753325495</v>
       </c>
       <c r="E30">
-        <v>-150.42</v>
+        <v>-140.7599999999999</v>
       </c>
       <c r="F30">
-        <v>270.48</v>
+        <v>280.14</v>
       </c>
       <c r="G30">
         <v>58.5</v>
@@ -3747,28 +3747,28 @@
         <v>119.775</v>
       </c>
       <c r="M30">
-        <v>14.47068</v>
+        <v>14.98749</v>
       </c>
       <c r="N30">
-        <v>105.30432</v>
+        <v>104.78751</v>
       </c>
       <c r="O30">
-        <v>25.27303679999999</v>
+        <v>25.14900239999999</v>
       </c>
       <c r="P30">
-        <v>80.03128319999999</v>
+        <v>79.63850759999998</v>
       </c>
       <c r="Q30">
-        <v>121.1312832</v>
+        <v>120.7385076</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1181313865549857</v>
+        <v>0.118961415995075</v>
       </c>
       <c r="T30">
-        <v>0.9956687618236906</v>
+        <v>1.007094429493738</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.27708165753095</v>
+        <v>7.991665048650571</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09625400535650327</v>
+        <v>0.09606861239341684</v>
       </c>
       <c r="C31">
-        <v>720.6859753325496</v>
+        <v>712.7289975983269</v>
       </c>
       <c r="D31">
-        <v>942.3259753325495</v>
+        <v>944.028997598327</v>
       </c>
       <c r="E31">
-        <v>-140.76</v>
+        <v>-131.1</v>
       </c>
       <c r="F31">
-        <v>280.14</v>
+        <v>289.8</v>
       </c>
       <c r="G31">
         <v>58.5</v>
@@ -3829,28 +3829,28 @@
         <v>119.775</v>
       </c>
       <c r="M31">
-        <v>14.98749</v>
+        <v>15.5043</v>
       </c>
       <c r="N31">
-        <v>104.78751</v>
+        <v>104.2707</v>
       </c>
       <c r="O31">
-        <v>25.14900239999999</v>
+        <v>25.02496799999999</v>
       </c>
       <c r="P31">
-        <v>79.6385076</v>
+        <v>79.24573199999998</v>
       </c>
       <c r="Q31">
-        <v>120.7385076</v>
+        <v>120.345732</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.118961415995075</v>
+        <v>0.1198151605620241</v>
       </c>
       <c r="T31">
-        <v>1.007094429493738</v>
+        <v>1.0188465448115</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.991665048650574</v>
+        <v>7.725276213695554</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09606861239341684</v>
+        <v>0.09607169943033043</v>
       </c>
       <c r="C32">
-        <v>712.7289975983269</v>
+        <v>703.0405896410659</v>
       </c>
       <c r="D32">
-        <v>944.028997598327</v>
+        <v>944.000589641066</v>
       </c>
       <c r="E32">
-        <v>-131.1</v>
+        <v>-121.44</v>
       </c>
       <c r="F32">
-        <v>289.8</v>
+        <v>299.46</v>
       </c>
       <c r="G32">
         <v>58.5</v>
@@ -3911,45 +3911,45 @@
         <v>119.775</v>
       </c>
       <c r="M32">
-        <v>15.5043</v>
+        <v>16.260678</v>
       </c>
       <c r="N32">
-        <v>104.2707</v>
+        <v>103.514322</v>
       </c>
       <c r="O32">
-        <v>25.02496799999999</v>
+        <v>24.84343727999999</v>
       </c>
       <c r="P32">
-        <v>79.24573199999998</v>
+        <v>78.67088471999999</v>
       </c>
       <c r="Q32">
-        <v>120.345732</v>
+        <v>119.77088472</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1198151605620241</v>
+        <v>0.120693651348305</v>
       </c>
       <c r="T32">
-        <v>1.0188465448115</v>
+        <v>1.030939301152966</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.725276213695554</v>
+        <v>7.365929022147784</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09607169943033043</v>
+        <v>0.095892386467244</v>
       </c>
       <c r="C33">
-        <v>703.0405896410659</v>
+        <v>695.0335277128598</v>
       </c>
       <c r="D33">
-        <v>944.000589641066</v>
+        <v>945.6535277128598</v>
       </c>
       <c r="E33">
-        <v>-121.44</v>
+        <v>-111.78</v>
       </c>
       <c r="F33">
-        <v>299.46</v>
+        <v>309.12</v>
       </c>
       <c r="G33">
         <v>58.5</v>
@@ -3993,28 +3993,28 @@
         <v>119.775</v>
       </c>
       <c r="M33">
-        <v>16.260678</v>
+        <v>16.785216</v>
       </c>
       <c r="N33">
-        <v>103.514322</v>
+        <v>102.989784</v>
       </c>
       <c r="O33">
-        <v>24.84343727999999</v>
+        <v>24.71754815999999</v>
       </c>
       <c r="P33">
-        <v>78.67088471999999</v>
+        <v>78.27223583999998</v>
       </c>
       <c r="Q33">
-        <v>119.77088472</v>
+        <v>119.37223584</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.120693651348305</v>
+        <v>0.1215979800988883</v>
       </c>
       <c r="T33">
-        <v>1.030939301152966</v>
+        <v>1.043387726798592</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.365929022147784</v>
+        <v>7.135743740205664</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.095892386467244</v>
+        <v>0.09571307350415757</v>
       </c>
       <c r="C34">
-        <v>695.0335277128598</v>
+        <v>687.0322645029182</v>
       </c>
       <c r="D34">
-        <v>945.6535277128598</v>
+        <v>947.3122645029182</v>
       </c>
       <c r="E34">
-        <v>-111.78</v>
+        <v>-102.1199999999999</v>
       </c>
       <c r="F34">
-        <v>309.12</v>
+        <v>318.78</v>
       </c>
       <c r="G34">
         <v>58.5</v>
@@ -4075,28 +4075,28 @@
         <v>119.775</v>
       </c>
       <c r="M34">
-        <v>16.785216</v>
+        <v>17.309754</v>
       </c>
       <c r="N34">
-        <v>102.989784</v>
+        <v>102.465246</v>
       </c>
       <c r="O34">
-        <v>24.71754815999999</v>
+        <v>24.59165903999999</v>
       </c>
       <c r="P34">
-        <v>78.27223583999998</v>
+        <v>77.87358695999998</v>
       </c>
       <c r="Q34">
-        <v>119.37223584</v>
+        <v>118.97358696</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1215979800988883</v>
+        <v>0.1225293037375486</v>
       </c>
       <c r="T34">
-        <v>1.043387726798592</v>
+        <v>1.056207747239611</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.135743740205664</v>
+        <v>6.919509081411554</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09571307350415757</v>
+        <v>0.09553376054107116</v>
       </c>
       <c r="C35">
-        <v>687.0322645029182</v>
+        <v>679.0368305788265</v>
       </c>
       <c r="D35">
-        <v>947.3122645029182</v>
+        <v>948.9768305788265</v>
       </c>
       <c r="E35">
-        <v>-102.1199999999999</v>
+        <v>-92.45999999999998</v>
       </c>
       <c r="F35">
-        <v>318.78</v>
+        <v>328.44</v>
       </c>
       <c r="G35">
         <v>58.5</v>
@@ -4157,28 +4157,28 @@
         <v>119.775</v>
       </c>
       <c r="M35">
-        <v>17.309754</v>
+        <v>17.834292</v>
       </c>
       <c r="N35">
-        <v>102.465246</v>
+        <v>101.940708</v>
       </c>
       <c r="O35">
-        <v>24.59165903999999</v>
+        <v>24.46576991999999</v>
       </c>
       <c r="P35">
-        <v>77.87358695999998</v>
+        <v>77.47493807999999</v>
       </c>
       <c r="Q35">
-        <v>118.97358696</v>
+        <v>118.57493808</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1225293037375486</v>
+        <v>0.1234888493046533</v>
       </c>
       <c r="T35">
-        <v>1.056207747239611</v>
+        <v>1.069416253148539</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.919509081411554</v>
+        <v>6.715994108428861</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09553376054107116</v>
+        <v>0.09535444757798474</v>
       </c>
       <c r="C36">
-        <v>679.0368305788265</v>
+        <v>671.047256723396</v>
       </c>
       <c r="D36">
-        <v>948.9768305788265</v>
+        <v>950.647256723396</v>
       </c>
       <c r="E36">
-        <v>-92.45999999999998</v>
+        <v>-82.79999999999995</v>
       </c>
       <c r="F36">
-        <v>328.44</v>
+        <v>338.1</v>
       </c>
       <c r="G36">
         <v>58.5</v>
@@ -4239,28 +4239,28 @@
         <v>119.775</v>
       </c>
       <c r="M36">
-        <v>17.834292</v>
+        <v>18.35883</v>
       </c>
       <c r="N36">
-        <v>101.940708</v>
+        <v>101.41617</v>
       </c>
       <c r="O36">
-        <v>24.46576991999999</v>
+        <v>24.3398808</v>
       </c>
       <c r="P36">
-        <v>77.47493807999999</v>
+        <v>77.07628919999999</v>
       </c>
       <c r="Q36">
-        <v>118.57493808</v>
+        <v>118.1762892</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1234888493046533</v>
+        <v>0.1244779193507458</v>
       </c>
       <c r="T36">
-        <v>1.069416253148539</v>
+        <v>1.083031174623896</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.715994108428861</v>
+        <v>6.524108562473751</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09535444757798474</v>
+        <v>0.09517513461489831</v>
       </c>
       <c r="C37">
-        <v>671.047256723396</v>
+        <v>663.0635739365605</v>
       </c>
       <c r="D37">
-        <v>950.647256723396</v>
+        <v>952.3235739365606</v>
       </c>
       <c r="E37">
-        <v>-82.79999999999995</v>
+        <v>-73.13999999999993</v>
       </c>
       <c r="F37">
-        <v>338.1</v>
+        <v>347.76</v>
       </c>
       <c r="G37">
         <v>58.5</v>
@@ -4321,28 +4321,28 @@
         <v>119.775</v>
       </c>
       <c r="M37">
-        <v>18.35883</v>
+        <v>18.883368</v>
       </c>
       <c r="N37">
-        <v>101.41617</v>
+        <v>100.891632</v>
       </c>
       <c r="O37">
-        <v>24.3398808</v>
+        <v>24.21399167999999</v>
       </c>
       <c r="P37">
-        <v>77.07628919999999</v>
+        <v>76.67764031999998</v>
       </c>
       <c r="Q37">
-        <v>118.1762892</v>
+        <v>117.77764032</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1244779193507458</v>
+        <v>0.1254978978357786</v>
       </c>
       <c r="T37">
-        <v>1.083031174623896</v>
+        <v>1.097071562395357</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.524108562473751</v>
+        <v>6.342883324627256</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09517513461489832</v>
+        <v>0.09499582165181189</v>
       </c>
       <c r="C38">
-        <v>663.0635739365606</v>
+        <v>655.0858134372941</v>
       </c>
       <c r="D38">
-        <v>952.3235739365606</v>
+        <v>954.005813437294</v>
       </c>
       <c r="E38">
-        <v>-73.13999999999999</v>
+        <v>-63.47999999999996</v>
       </c>
       <c r="F38">
-        <v>347.76</v>
+        <v>357.42</v>
       </c>
       <c r="G38">
         <v>58.5</v>
@@ -4403,28 +4403,28 @@
         <v>119.775</v>
       </c>
       <c r="M38">
-        <v>18.883368</v>
+        <v>19.407906</v>
       </c>
       <c r="N38">
-        <v>100.891632</v>
+        <v>100.367094</v>
       </c>
       <c r="O38">
-        <v>24.21399167999999</v>
+        <v>24.08810256</v>
       </c>
       <c r="P38">
-        <v>76.67764031999998</v>
+        <v>76.27899143999998</v>
       </c>
       <c r="Q38">
-        <v>117.77764032</v>
+        <v>117.37899144</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1254978978357786</v>
+        <v>0.1265502565901776</v>
       </c>
       <c r="T38">
-        <v>1.097071562395357</v>
+        <v>1.111557676762738</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.342883324627258</v>
+        <v>6.171454045583278</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09499582165181189</v>
+        <v>0.09510530868872547</v>
       </c>
       <c r="C39">
-        <v>655.0858134372941</v>
+        <v>644.3979458840961</v>
       </c>
       <c r="D39">
-        <v>954.005813437294</v>
+        <v>952.977945884096</v>
       </c>
       <c r="E39">
-        <v>-63.47999999999996</v>
+        <v>-53.81999999999999</v>
       </c>
       <c r="F39">
-        <v>357.42</v>
+        <v>367.08</v>
       </c>
       <c r="G39">
         <v>58.5</v>
@@ -4485,45 +4485,45 @@
         <v>119.775</v>
       </c>
       <c r="M39">
-        <v>19.407906</v>
+        <v>20.299524</v>
       </c>
       <c r="N39">
-        <v>100.367094</v>
+        <v>99.47547599999999</v>
       </c>
       <c r="O39">
-        <v>24.08810256</v>
+        <v>23.87411424</v>
       </c>
       <c r="P39">
-        <v>76.27899143999998</v>
+        <v>75.60136175999999</v>
       </c>
       <c r="Q39">
-        <v>117.37899144</v>
+        <v>116.70136176</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1265502565901776</v>
+        <v>0.1276365624011701</v>
       </c>
       <c r="T39">
-        <v>1.111557676762738</v>
+        <v>1.12651108514197</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.171454045583278</v>
+        <v>5.900384659265902</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09510530868872547</v>
+        <v>0.09493359572563904</v>
       </c>
       <c r="C40">
-        <v>644.3979458840961</v>
+        <v>636.3509810759455</v>
       </c>
       <c r="D40">
-        <v>952.977945884096</v>
+        <v>954.5909810759455</v>
       </c>
       <c r="E40">
-        <v>-53.81999999999999</v>
+        <v>-44.15999999999997</v>
       </c>
       <c r="F40">
-        <v>367.08</v>
+        <v>376.74</v>
       </c>
       <c r="G40">
         <v>58.5</v>
@@ -4567,28 +4567,28 @@
         <v>119.775</v>
       </c>
       <c r="M40">
-        <v>20.299524</v>
+        <v>20.833722</v>
       </c>
       <c r="N40">
-        <v>99.47547599999999</v>
+        <v>98.94127799999998</v>
       </c>
       <c r="O40">
-        <v>23.87411424</v>
+        <v>23.74590671999999</v>
       </c>
       <c r="P40">
-        <v>75.60136175999999</v>
+        <v>75.19537127999999</v>
       </c>
       <c r="Q40">
-        <v>116.70136176</v>
+        <v>116.29537128</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1276365624011701</v>
+        <v>0.1287584847961296</v>
       </c>
       <c r="T40">
-        <v>1.12651108514197</v>
+        <v>1.141954769205767</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.900384659265902</v>
+        <v>5.74909274492575</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09493359572563904</v>
+        <v>0.09476188276255264</v>
       </c>
       <c r="C41">
-        <v>636.3509810759455</v>
+        <v>628.3094860565179</v>
       </c>
       <c r="D41">
-        <v>954.5909810759455</v>
+        <v>956.209486056518</v>
       </c>
       <c r="E41">
-        <v>-44.15999999999997</v>
+        <v>-34.49999999999994</v>
       </c>
       <c r="F41">
-        <v>376.74</v>
+        <v>386.4</v>
       </c>
       <c r="G41">
         <v>58.5</v>
@@ -4649,28 +4649,28 @@
         <v>119.775</v>
       </c>
       <c r="M41">
-        <v>20.833722</v>
+        <v>21.36792</v>
       </c>
       <c r="N41">
-        <v>98.94127799999998</v>
+        <v>98.40707999999998</v>
       </c>
       <c r="O41">
-        <v>23.74590671999999</v>
+        <v>23.61769919999999</v>
       </c>
       <c r="P41">
-        <v>75.19537127999999</v>
+        <v>74.78938079999999</v>
       </c>
       <c r="Q41">
-        <v>116.29537128</v>
+        <v>115.8893808</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1287584847961296</v>
+        <v>0.1299178046042544</v>
       </c>
       <c r="T41">
-        <v>1.141954769205767</v>
+        <v>1.157913242738357</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.74909274492575</v>
+        <v>5.605365426302606</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09476188276255264</v>
+        <v>0.0945901697994662</v>
       </c>
       <c r="C42">
-        <v>628.3094860565179</v>
+        <v>620.2734886950775</v>
       </c>
       <c r="D42">
-        <v>956.209486056518</v>
+        <v>957.8334886950776</v>
       </c>
       <c r="E42">
-        <v>-34.49999999999994</v>
+        <v>-24.83999999999997</v>
       </c>
       <c r="F42">
-        <v>386.4</v>
+        <v>396.06</v>
       </c>
       <c r="G42">
         <v>58.5</v>
@@ -4731,28 +4731,28 @@
         <v>119.775</v>
       </c>
       <c r="M42">
-        <v>21.36792</v>
+        <v>21.902118</v>
       </c>
       <c r="N42">
-        <v>98.40707999999998</v>
+        <v>97.87288199999998</v>
       </c>
       <c r="O42">
-        <v>23.61769919999999</v>
+        <v>23.48949167999999</v>
       </c>
       <c r="P42">
-        <v>74.78938079999999</v>
+        <v>74.38339031999999</v>
       </c>
       <c r="Q42">
-        <v>115.8893808</v>
+        <v>115.48339032</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1299178046042544</v>
+        <v>0.1311164233889258</v>
       </c>
       <c r="T42">
-        <v>1.157913242738357</v>
+        <v>1.174412681475442</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.605365426302606</v>
+        <v>5.468649196392786</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0945901697994662</v>
+        <v>0.09441845683637978</v>
       </c>
       <c r="C43">
-        <v>620.2734886950775</v>
+        <v>612.243017050539</v>
       </c>
       <c r="D43">
-        <v>957.8334886950776</v>
+        <v>959.4630170505391</v>
       </c>
       <c r="E43">
-        <v>-24.83999999999997</v>
+        <v>-15.17999999999995</v>
       </c>
       <c r="F43">
-        <v>396.06</v>
+        <v>405.72</v>
       </c>
       <c r="G43">
         <v>58.5</v>
@@ -4813,28 +4813,28 @@
         <v>119.775</v>
       </c>
       <c r="M43">
-        <v>21.902118</v>
+        <v>22.436316</v>
       </c>
       <c r="N43">
-        <v>97.87288199999998</v>
+        <v>97.33868399999997</v>
       </c>
       <c r="O43">
-        <v>23.48949167999999</v>
+        <v>23.36128415999999</v>
       </c>
       <c r="P43">
-        <v>74.38339031999999</v>
+        <v>73.97739983999998</v>
       </c>
       <c r="Q43">
-        <v>115.48339032</v>
+        <v>115.07739984</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1311164233889258</v>
+        <v>0.1323563738558272</v>
       </c>
       <c r="T43">
-        <v>1.174412681475442</v>
+        <v>1.191481066375875</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.468649196392786</v>
+        <v>5.338443263145338</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09441845683637978</v>
+        <v>0.09424674387329335</v>
       </c>
       <c r="C44">
-        <v>612.243017050539</v>
+        <v>604.2180993730859</v>
       </c>
       <c r="D44">
-        <v>959.4630170505391</v>
+        <v>961.0980993730859</v>
       </c>
       <c r="E44">
-        <v>-15.18000000000001</v>
+        <v>-5.519999999999982</v>
       </c>
       <c r="F44">
-        <v>405.72</v>
+        <v>415.38</v>
       </c>
       <c r="G44">
         <v>58.5</v>
@@ -4895,28 +4895,28 @@
         <v>119.775</v>
       </c>
       <c r="M44">
-        <v>22.436316</v>
+        <v>22.970514</v>
       </c>
       <c r="N44">
-        <v>97.33868399999997</v>
+        <v>96.80448599999997</v>
       </c>
       <c r="O44">
-        <v>23.36128415999999</v>
+        <v>23.23307663999999</v>
       </c>
       <c r="P44">
-        <v>73.97739983999998</v>
+        <v>73.57140935999998</v>
       </c>
       <c r="Q44">
-        <v>115.07739984</v>
+        <v>114.67140936</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1323563738558272</v>
+        <v>0.133639831356655</v>
       </c>
       <c r="T44">
-        <v>1.191481066375874</v>
+        <v>1.209148341974568</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.338443263145339</v>
+        <v>5.214293419816377</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09424674387329335</v>
+        <v>0.09407503091020693</v>
       </c>
       <c r="C45">
-        <v>604.2180993730859</v>
+        <v>596.1987641058015</v>
       </c>
       <c r="D45">
-        <v>961.0980993730859</v>
+        <v>962.7387641058016</v>
       </c>
       <c r="E45">
-        <v>-5.519999999999982</v>
+        <v>4.140000000000043</v>
       </c>
       <c r="F45">
-        <v>415.38</v>
+        <v>425.04</v>
       </c>
       <c r="G45">
         <v>58.5</v>
@@ -4977,28 +4977,28 @@
         <v>119.775</v>
       </c>
       <c r="M45">
-        <v>22.970514</v>
+        <v>23.504712</v>
       </c>
       <c r="N45">
-        <v>96.80448599999997</v>
+        <v>96.27028799999998</v>
       </c>
       <c r="O45">
-        <v>23.23307663999999</v>
+        <v>23.10486911999999</v>
       </c>
       <c r="P45">
-        <v>73.57140935999998</v>
+        <v>73.16541887999999</v>
       </c>
       <c r="Q45">
-        <v>114.67140936</v>
+        <v>114.26541888</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.133639831356655</v>
+        <v>0.1349691266253695</v>
       </c>
       <c r="T45">
-        <v>1.209148341974568</v>
+        <v>1.227446591701786</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.214293419816377</v>
+        <v>5.095786751184187</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09407503091020693</v>
+        <v>0.09390331794712052</v>
       </c>
       <c r="C46">
-        <v>596.1987641058015</v>
+        <v>588.1850398863196</v>
       </c>
       <c r="D46">
-        <v>962.7387641058016</v>
+        <v>964.3850398863196</v>
       </c>
       <c r="E46">
-        <v>4.140000000000043</v>
+        <v>13.80000000000001</v>
       </c>
       <c r="F46">
-        <v>425.04</v>
+        <v>434.7</v>
       </c>
       <c r="G46">
         <v>58.5</v>
@@ -5059,28 +5059,28 @@
         <v>119.775</v>
       </c>
       <c r="M46">
-        <v>23.504712</v>
+        <v>24.03891</v>
       </c>
       <c r="N46">
-        <v>96.27028799999998</v>
+        <v>95.73608999999998</v>
       </c>
       <c r="O46">
-        <v>23.10486911999999</v>
+        <v>22.97666159999999</v>
       </c>
       <c r="P46">
-        <v>73.16541887999999</v>
+        <v>72.75942839999999</v>
       </c>
       <c r="Q46">
-        <v>114.26541888</v>
+        <v>113.8594284</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1349691266253695</v>
+        <v>0.1363467599038555</v>
       </c>
       <c r="T46">
-        <v>1.227446591701786</v>
+        <v>1.246410232328175</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.095786751184187</v>
+        <v>4.982547045602316</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09390331794712052</v>
+        <v>0.0937316049840341</v>
       </c>
       <c r="C47">
-        <v>588.1850398863196</v>
+        <v>580.1769555484904</v>
       </c>
       <c r="D47">
-        <v>964.3850398863196</v>
+        <v>966.0369555484903</v>
       </c>
       <c r="E47">
-        <v>13.80000000000001</v>
+        <v>23.46000000000004</v>
       </c>
       <c r="F47">
-        <v>434.7</v>
+        <v>444.36</v>
       </c>
       <c r="G47">
         <v>58.5</v>
@@ -5141,28 +5141,28 @@
         <v>119.775</v>
       </c>
       <c r="M47">
-        <v>24.03891</v>
+        <v>24.573108</v>
       </c>
       <c r="N47">
-        <v>95.73608999999998</v>
+        <v>95.20189199999997</v>
       </c>
       <c r="O47">
-        <v>22.97666159999999</v>
+        <v>22.84845407999999</v>
       </c>
       <c r="P47">
-        <v>72.75942839999999</v>
+        <v>72.35343791999998</v>
       </c>
       <c r="Q47">
-        <v>113.8594284</v>
+        <v>113.45343792</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1363467599038555</v>
+        <v>0.1377754166371002</v>
       </c>
       <c r="T47">
-        <v>1.246410232328175</v>
+        <v>1.266076230014802</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.982547045602316</v>
+        <v>4.874230805480527</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0937316049840341</v>
+        <v>0.09355989202094767</v>
       </c>
       <c r="C48">
-        <v>580.1769555484904</v>
+        <v>572.1745401240623</v>
       </c>
       <c r="D48">
-        <v>966.0369555484903</v>
+        <v>967.6945401240623</v>
       </c>
       <c r="E48">
-        <v>23.46000000000004</v>
+        <v>33.12000000000006</v>
       </c>
       <c r="F48">
-        <v>444.36</v>
+        <v>454.02</v>
       </c>
       <c r="G48">
         <v>58.5</v>
@@ -5223,28 +5223,28 @@
         <v>119.775</v>
       </c>
       <c r="M48">
-        <v>24.573108</v>
+        <v>25.107306</v>
       </c>
       <c r="N48">
-        <v>95.20189199999997</v>
+        <v>94.66769399999997</v>
       </c>
       <c r="O48">
-        <v>22.84845407999999</v>
+        <v>22.72024655999999</v>
       </c>
       <c r="P48">
-        <v>72.35343791999998</v>
+        <v>71.94744743999998</v>
       </c>
       <c r="Q48">
-        <v>113.45343792</v>
+        <v>113.04744744</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1377754166371002</v>
+        <v>0.1392579849451843</v>
       </c>
       <c r="T48">
-        <v>1.266076230014802</v>
+        <v>1.286484340821678</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.874230805480527</v>
+        <v>4.770523767066047</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09355989202094767</v>
+        <v>0.09338817905786125</v>
       </c>
       <c r="C49">
-        <v>572.1745401240623</v>
+        <v>564.1778228443848</v>
       </c>
       <c r="D49">
-        <v>967.6945401240623</v>
+        <v>969.3578228443848</v>
       </c>
       <c r="E49">
-        <v>33.12000000000006</v>
+        <v>42.78000000000009</v>
       </c>
       <c r="F49">
-        <v>454.02</v>
+        <v>463.6800000000001</v>
       </c>
       <c r="G49">
         <v>58.5</v>
@@ -5305,28 +5305,28 @@
         <v>119.775</v>
       </c>
       <c r="M49">
-        <v>25.107306</v>
+        <v>25.641504</v>
       </c>
       <c r="N49">
-        <v>94.66769399999997</v>
+        <v>94.13349599999998</v>
       </c>
       <c r="O49">
-        <v>22.72024655999999</v>
+        <v>22.59203904</v>
       </c>
       <c r="P49">
-        <v>71.94744743999998</v>
+        <v>71.54145695999998</v>
       </c>
       <c r="Q49">
-        <v>113.04744744</v>
+        <v>112.64145696</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1392579849451843</v>
+        <v>0.1407975751112716</v>
       </c>
       <c r="T49">
-        <v>1.286484340821678</v>
+        <v>1.30767737896728</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.770523767066047</v>
+        <v>4.671137855252171</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09338817905786125</v>
+        <v>0.0932164660947748</v>
       </c>
       <c r="C50">
-        <v>564.1778228443848</v>
+        <v>556.1868331421265</v>
       </c>
       <c r="D50">
-        <v>969.3578228443848</v>
+        <v>971.0268331421264</v>
       </c>
       <c r="E50">
-        <v>42.78000000000003</v>
+        <v>52.44</v>
       </c>
       <c r="F50">
-        <v>463.68</v>
+        <v>473.34</v>
       </c>
       <c r="G50">
         <v>58.5</v>
@@ -5387,28 +5387,28 @@
         <v>119.775</v>
       </c>
       <c r="M50">
-        <v>25.641504</v>
+        <v>26.175702</v>
       </c>
       <c r="N50">
-        <v>94.13349599999998</v>
+        <v>93.59929799999998</v>
       </c>
       <c r="O50">
-        <v>22.59203904</v>
+        <v>22.46383151999999</v>
       </c>
       <c r="P50">
-        <v>71.54145695999998</v>
+        <v>71.13546647999999</v>
       </c>
       <c r="Q50">
-        <v>112.64145696</v>
+        <v>112.23546648</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1407975751112716</v>
+        <v>0.1423975413623035</v>
       </c>
       <c r="T50">
-        <v>1.30767737896728</v>
+        <v>1.329701516648004</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.671137855252171</v>
+        <v>4.575808511267433</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0932164660947748</v>
+        <v>0.09399475313168838</v>
       </c>
       <c r="C51">
-        <v>556.1868331421265</v>
+        <v>539.0077167330076</v>
       </c>
       <c r="D51">
-        <v>971.0268331421264</v>
+        <v>963.5077167330076</v>
       </c>
       <c r="E51">
-        <v>52.44</v>
+        <v>62.10000000000002</v>
       </c>
       <c r="F51">
-        <v>473.34</v>
+        <v>483</v>
       </c>
       <c r="G51">
         <v>58.5</v>
@@ -5469,45 +5469,45 @@
         <v>119.775</v>
       </c>
       <c r="M51">
-        <v>26.175702</v>
+        <v>27.9174</v>
       </c>
       <c r="N51">
-        <v>93.59929799999998</v>
+        <v>91.85759999999998</v>
       </c>
       <c r="O51">
-        <v>22.46383151999999</v>
+        <v>22.04582399999999</v>
       </c>
       <c r="P51">
-        <v>71.13546647999999</v>
+        <v>69.81177599999998</v>
       </c>
       <c r="Q51">
-        <v>112.23546648</v>
+        <v>110.911776</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1423975413623035</v>
+        <v>0.1440615062633768</v>
       </c>
       <c r="T51">
-        <v>1.329701516648004</v>
+        <v>1.352606619835957</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.575808511267433</v>
+        <v>4.290335059855144</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09399475313168838</v>
+        <v>0.09384204016860197</v>
       </c>
       <c r="C52">
-        <v>539.0077167330076</v>
+        <v>530.8138965930834</v>
       </c>
       <c r="D52">
-        <v>963.5077167330076</v>
+        <v>964.9738965930834</v>
       </c>
       <c r="E52">
-        <v>62.10000000000002</v>
+        <v>71.76000000000005</v>
       </c>
       <c r="F52">
-        <v>483</v>
+        <v>492.66</v>
       </c>
       <c r="G52">
         <v>58.5</v>
@@ -5551,28 +5551,28 @@
         <v>119.775</v>
       </c>
       <c r="M52">
-        <v>27.9174</v>
+        <v>28.475748</v>
       </c>
       <c r="N52">
-        <v>91.85759999999998</v>
+        <v>91.29925199999997</v>
       </c>
       <c r="O52">
-        <v>22.04582399999999</v>
+        <v>21.91182047999999</v>
       </c>
       <c r="P52">
-        <v>69.81177599999998</v>
+        <v>69.38743151999998</v>
       </c>
       <c r="Q52">
-        <v>110.911776</v>
+        <v>110.48743152</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1440615062633768</v>
+        <v>0.1457933880991877</v>
       </c>
       <c r="T52">
-        <v>1.352606619835957</v>
+        <v>1.376446625194847</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.290335059855144</v>
+        <v>4.206210842995238</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09384204016860197</v>
+        <v>0.09368932720551554</v>
       </c>
       <c r="C53">
-        <v>530.8138965930834</v>
+        <v>522.6245454564189</v>
       </c>
       <c r="D53">
-        <v>964.9738965930834</v>
+        <v>966.444545456419</v>
       </c>
       <c r="E53">
-        <v>71.76000000000005</v>
+        <v>81.42000000000002</v>
       </c>
       <c r="F53">
-        <v>492.66</v>
+        <v>502.32</v>
       </c>
       <c r="G53">
         <v>58.5</v>
@@ -5633,28 +5633,28 @@
         <v>119.775</v>
       </c>
       <c r="M53">
-        <v>28.475748</v>
+        <v>29.034096</v>
       </c>
       <c r="N53">
-        <v>91.29925199999997</v>
+        <v>90.74090399999997</v>
       </c>
       <c r="O53">
-        <v>21.91182047999999</v>
+        <v>21.77781695999999</v>
       </c>
       <c r="P53">
-        <v>69.38743151999998</v>
+        <v>68.96308703999998</v>
       </c>
       <c r="Q53">
-        <v>110.48743152</v>
+        <v>110.06308704</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1457933880991877</v>
+        <v>0.1475974316781574</v>
       </c>
       <c r="T53">
-        <v>1.376446625194847</v>
+        <v>1.401279964110357</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.206210842995238</v>
+        <v>4.125322172937637</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09368932720551554</v>
+        <v>0.09353661424242911</v>
       </c>
       <c r="C54">
-        <v>522.6245454564189</v>
+        <v>514.4396837868826</v>
       </c>
       <c r="D54">
-        <v>966.444545456419</v>
+        <v>967.9196837868827</v>
       </c>
       <c r="E54">
-        <v>81.42000000000002</v>
+        <v>91.08000000000004</v>
       </c>
       <c r="F54">
-        <v>502.32</v>
+        <v>511.98</v>
       </c>
       <c r="G54">
         <v>58.5</v>
@@ -5715,28 +5715,28 @@
         <v>119.775</v>
       </c>
       <c r="M54">
-        <v>29.034096</v>
+        <v>29.592444</v>
       </c>
       <c r="N54">
-        <v>90.74090399999997</v>
+        <v>90.18255599999998</v>
       </c>
       <c r="O54">
-        <v>21.77781695999999</v>
+        <v>21.64381344</v>
       </c>
       <c r="P54">
-        <v>68.96308703999998</v>
+        <v>68.53874255999997</v>
       </c>
       <c r="Q54">
-        <v>110.06308704</v>
+        <v>109.63874256</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1475974316781574</v>
+        <v>0.1494782430689981</v>
       </c>
       <c r="T54">
-        <v>1.401279964110357</v>
+        <v>1.427170040852059</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.125322172937637</v>
+        <v>4.04748590552372</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09353661424242911</v>
+        <v>0.0948203012793427</v>
       </c>
       <c r="C55">
-        <v>514.4396837868826</v>
+        <v>492.5182383885757</v>
       </c>
       <c r="D55">
-        <v>967.9196837868827</v>
+        <v>955.6582383885757</v>
       </c>
       <c r="E55">
-        <v>91.08000000000004</v>
+        <v>100.74</v>
       </c>
       <c r="F55">
-        <v>511.98</v>
+        <v>521.64</v>
       </c>
       <c r="G55">
         <v>58.5</v>
@@ -5797,45 +5797,45 @@
         <v>119.775</v>
       </c>
       <c r="M55">
-        <v>29.592444</v>
+        <v>31.976532</v>
       </c>
       <c r="N55">
-        <v>90.18255599999998</v>
+        <v>87.79846799999999</v>
       </c>
       <c r="O55">
-        <v>21.64381344</v>
+        <v>21.07163232</v>
       </c>
       <c r="P55">
-        <v>68.53874255999997</v>
+        <v>66.72683567999999</v>
       </c>
       <c r="Q55">
-        <v>109.63874256</v>
+        <v>107.82683568</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1494782430689981</v>
+        <v>0.1514408288681363</v>
       </c>
       <c r="T55">
-        <v>1.427170040852059</v>
+        <v>1.45418577310427</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.04748590552372</v>
+        <v>3.745715764298642</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0948203012793427</v>
+        <v>0.09469418831625628</v>
       </c>
       <c r="C56">
-        <v>492.5182383885757</v>
+        <v>484.0490590326908</v>
       </c>
       <c r="D56">
-        <v>955.6582383885757</v>
+        <v>956.8490590326909</v>
       </c>
       <c r="E56">
-        <v>100.74</v>
+        <v>110.4000000000001</v>
       </c>
       <c r="F56">
-        <v>521.64</v>
+        <v>531.3000000000001</v>
       </c>
       <c r="G56">
         <v>58.5</v>
@@ -5879,28 +5879,28 @@
         <v>119.775</v>
       </c>
       <c r="M56">
-        <v>31.976532</v>
+        <v>32.56869</v>
       </c>
       <c r="N56">
-        <v>87.79846799999999</v>
+        <v>87.20630999999997</v>
       </c>
       <c r="O56">
-        <v>21.07163232</v>
+        <v>20.92951439999999</v>
       </c>
       <c r="P56">
-        <v>66.72683567999999</v>
+        <v>66.27679559999999</v>
       </c>
       <c r="Q56">
-        <v>107.82683568</v>
+        <v>107.3767956</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1514408288681363</v>
+        <v>0.1534906407027918</v>
       </c>
       <c r="T56">
-        <v>1.45418577310427</v>
+        <v>1.482402204567691</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.745715764298642</v>
+        <v>3.677611841311393</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09469418831625628</v>
+        <v>0.09456807535316986</v>
       </c>
       <c r="C57">
-        <v>484.0490590326908</v>
+        <v>475.5828510800831</v>
       </c>
       <c r="D57">
-        <v>956.8490590326909</v>
+        <v>958.0428510800831</v>
       </c>
       <c r="E57">
-        <v>110.4000000000001</v>
+        <v>120.0600000000001</v>
       </c>
       <c r="F57">
-        <v>531.3000000000001</v>
+        <v>540.96</v>
       </c>
       <c r="G57">
         <v>58.5</v>
@@ -5961,28 +5961,28 @@
         <v>119.775</v>
       </c>
       <c r="M57">
-        <v>32.56869</v>
+        <v>33.160848</v>
       </c>
       <c r="N57">
-        <v>87.20630999999997</v>
+        <v>86.61415199999998</v>
       </c>
       <c r="O57">
-        <v>20.92951439999999</v>
+        <v>20.78739647999999</v>
       </c>
       <c r="P57">
-        <v>66.27679559999999</v>
+        <v>65.82675551999998</v>
       </c>
       <c r="Q57">
-        <v>107.3767956</v>
+        <v>106.92675552</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1534906407027918</v>
+        <v>0.1556336258026588</v>
       </c>
       <c r="T57">
-        <v>1.482402204567691</v>
+        <v>1.51190120109763</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.677611841311393</v>
+        <v>3.611940201287976</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09456807535316986</v>
+        <v>0.09444196239008343</v>
       </c>
       <c r="C58">
-        <v>475.5828510800831</v>
+        <v>467.1196256662668</v>
       </c>
       <c r="D58">
-        <v>958.0428510800831</v>
+        <v>959.2396256662668</v>
       </c>
       <c r="E58">
-        <v>120.0600000000001</v>
+        <v>129.72</v>
       </c>
       <c r="F58">
-        <v>540.96</v>
+        <v>550.62</v>
       </c>
       <c r="G58">
         <v>58.5</v>
@@ -6043,28 +6043,28 @@
         <v>119.775</v>
       </c>
       <c r="M58">
-        <v>33.160848</v>
+        <v>33.753006</v>
       </c>
       <c r="N58">
-        <v>86.61415199999998</v>
+        <v>86.02199399999998</v>
       </c>
       <c r="O58">
-        <v>20.78739647999999</v>
+        <v>20.64527855999999</v>
       </c>
       <c r="P58">
-        <v>65.82675551999998</v>
+        <v>65.37671543999998</v>
       </c>
       <c r="Q58">
-        <v>106.92675552</v>
+        <v>106.47671544</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1556336258026588</v>
+        <v>0.157876284628101</v>
       </c>
       <c r="T58">
-        <v>1.51190120109763</v>
+        <v>1.542772243977799</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.611940201287976</v>
+        <v>3.548572829335555</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09444196239008343</v>
+        <v>0.095550089426997</v>
       </c>
       <c r="C59">
-        <v>467.1196256662668</v>
+        <v>447.0450071240508</v>
       </c>
       <c r="D59">
-        <v>959.2396256662668</v>
+        <v>948.8250071240509</v>
       </c>
       <c r="E59">
-        <v>129.72</v>
+        <v>139.3800000000001</v>
       </c>
       <c r="F59">
-        <v>550.62</v>
+        <v>560.2800000000001</v>
       </c>
       <c r="G59">
         <v>58.5</v>
@@ -6125,45 +6125,45 @@
         <v>119.775</v>
       </c>
       <c r="M59">
-        <v>33.753006</v>
+        <v>35.913948</v>
       </c>
       <c r="N59">
-        <v>86.02199399999998</v>
+        <v>83.86105199999997</v>
       </c>
       <c r="O59">
-        <v>20.64527855999999</v>
+        <v>20.12665247999999</v>
       </c>
       <c r="P59">
-        <v>65.37671543999998</v>
+        <v>63.73439951999998</v>
       </c>
       <c r="Q59">
-        <v>106.47671544</v>
+        <v>104.83439952</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.157876284628101</v>
+        <v>0.1602257367309453</v>
       </c>
       <c r="T59">
-        <v>1.542772243977799</v>
+        <v>1.575113336518928</v>
       </c>
       <c r="U59">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.548572829335555</v>
+        <v>3.335055227010964</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09555008942699703</v>
+        <v>0.09544525646391058</v>
       </c>
       <c r="C60">
-        <v>447.0450071240508</v>
+        <v>438.3605738838705</v>
       </c>
       <c r="D60">
-        <v>948.8250071240508</v>
+        <v>949.8005738838705</v>
       </c>
       <c r="E60">
-        <v>139.38</v>
+        <v>149.04</v>
       </c>
       <c r="F60">
-        <v>560.28</v>
+        <v>569.9399999999999</v>
       </c>
       <c r="G60">
         <v>58.5</v>
@@ -6207,28 +6207,28 @@
         <v>119.775</v>
       </c>
       <c r="M60">
-        <v>35.913948</v>
+        <v>36.533154</v>
       </c>
       <c r="N60">
-        <v>83.86105199999997</v>
+        <v>83.24184599999998</v>
       </c>
       <c r="O60">
-        <v>20.12665247999999</v>
+        <v>19.97804304</v>
       </c>
       <c r="P60">
-        <v>63.73439951999998</v>
+        <v>63.26380295999999</v>
       </c>
       <c r="Q60">
-        <v>104.83439952</v>
+        <v>104.36380296</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1602257367309453</v>
+        <v>0.1626897962534405</v>
       </c>
       <c r="T60">
-        <v>1.575113336518928</v>
+        <v>1.609032043330357</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.335055227010965</v>
+        <v>3.278528867231118</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09544525646391058</v>
+        <v>0.09534042350082417</v>
       </c>
       <c r="C61">
-        <v>438.3605738838705</v>
+        <v>429.6781488328859</v>
       </c>
       <c r="D61">
-        <v>949.8005738838705</v>
+        <v>950.7781488328859</v>
       </c>
       <c r="E61">
-        <v>149.04</v>
+        <v>158.7</v>
       </c>
       <c r="F61">
-        <v>569.9399999999999</v>
+        <v>579.6</v>
       </c>
       <c r="G61">
         <v>58.5</v>
@@ -6289,28 +6289,28 @@
         <v>119.775</v>
       </c>
       <c r="M61">
-        <v>36.533154</v>
+        <v>37.15236</v>
       </c>
       <c r="N61">
-        <v>83.24184599999998</v>
+        <v>82.62263999999998</v>
       </c>
       <c r="O61">
-        <v>19.97804304</v>
+        <v>19.82943359999999</v>
       </c>
       <c r="P61">
-        <v>63.26380295999999</v>
+        <v>62.79320639999998</v>
       </c>
       <c r="Q61">
-        <v>104.36380296</v>
+        <v>103.8932064</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1626897962534405</v>
+        <v>0.1652770587520604</v>
       </c>
       <c r="T61">
-        <v>1.609032043330357</v>
+        <v>1.644646685482357</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.278528867231118</v>
+        <v>3.223886719443932</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09534042350082417</v>
+        <v>0.09523559053773775</v>
       </c>
       <c r="C62">
-        <v>429.6781488328859</v>
+        <v>420.9977381782264</v>
       </c>
       <c r="D62">
-        <v>950.7781488328859</v>
+        <v>951.7577381782264</v>
       </c>
       <c r="E62">
-        <v>158.7</v>
+        <v>168.36</v>
       </c>
       <c r="F62">
-        <v>579.6</v>
+        <v>589.26</v>
       </c>
       <c r="G62">
         <v>58.5</v>
@@ -6371,28 +6371,28 @@
         <v>119.775</v>
       </c>
       <c r="M62">
-        <v>37.15236</v>
+        <v>37.771566</v>
       </c>
       <c r="N62">
-        <v>82.62263999999998</v>
+        <v>82.00343399999997</v>
       </c>
       <c r="O62">
-        <v>19.82943359999999</v>
+        <v>19.68082415999999</v>
       </c>
       <c r="P62">
-        <v>62.79320639999998</v>
+        <v>62.32260983999998</v>
       </c>
       <c r="Q62">
-        <v>103.8932064</v>
+        <v>103.42260984</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1652770587520604</v>
+        <v>0.1679970013788147</v>
       </c>
       <c r="T62">
-        <v>1.644646685482357</v>
+        <v>1.682087719539588</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.223886719443932</v>
+        <v>3.171036117485835</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09523559053773775</v>
+        <v>0.09513075757465131</v>
       </c>
       <c r="C63">
-        <v>420.9977381782264</v>
+        <v>412.3193481526275</v>
       </c>
       <c r="D63">
-        <v>951.7577381782264</v>
+        <v>952.7393481526275</v>
       </c>
       <c r="E63">
-        <v>168.36</v>
+        <v>178.02</v>
       </c>
       <c r="F63">
-        <v>589.26</v>
+        <v>598.92</v>
       </c>
       <c r="G63">
         <v>58.5</v>
@@ -6453,28 +6453,28 @@
         <v>119.775</v>
       </c>
       <c r="M63">
-        <v>37.771566</v>
+        <v>38.390772</v>
       </c>
       <c r="N63">
-        <v>82.00343399999997</v>
+        <v>81.38422799999998</v>
       </c>
       <c r="O63">
-        <v>19.68082415999999</v>
+        <v>19.53221472</v>
       </c>
       <c r="P63">
-        <v>62.32260983999998</v>
+        <v>61.85201327999998</v>
       </c>
       <c r="Q63">
-        <v>103.42260984</v>
+        <v>102.95201328</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1679970013788147</v>
+        <v>0.1708600988806614</v>
       </c>
       <c r="T63">
-        <v>1.682087719539588</v>
+        <v>1.721499334336673</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.171036117485835</v>
+        <v>3.119890373655418</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09513075757465131</v>
+        <v>0.09502592461156489</v>
       </c>
       <c r="C64">
-        <v>412.3193481526275</v>
+        <v>403.6429850145645</v>
       </c>
       <c r="D64">
-        <v>952.7393481526275</v>
+        <v>953.7229850145645</v>
       </c>
       <c r="E64">
-        <v>178.02</v>
+        <v>187.6800000000001</v>
       </c>
       <c r="F64">
-        <v>598.92</v>
+        <v>608.58</v>
       </c>
       <c r="G64">
         <v>58.5</v>
@@ -6535,28 +6535,28 @@
         <v>119.775</v>
       </c>
       <c r="M64">
-        <v>38.390772</v>
+        <v>39.009978</v>
       </c>
       <c r="N64">
-        <v>81.38422799999998</v>
+        <v>80.76502199999997</v>
       </c>
       <c r="O64">
-        <v>19.53221472</v>
+        <v>19.38360527999999</v>
       </c>
       <c r="P64">
-        <v>61.85201327999998</v>
+        <v>61.38141671999998</v>
       </c>
       <c r="Q64">
-        <v>102.95201328</v>
+        <v>102.48141672</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1708600988806614</v>
+        <v>0.1738779584096349</v>
       </c>
       <c r="T64">
-        <v>1.721499334336673</v>
+        <v>1.763041306690357</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.119890373655418</v>
+        <v>3.070368304232316</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09502592461156489</v>
+        <v>0.09492109164847848</v>
       </c>
       <c r="C65">
-        <v>403.6429850145645</v>
+        <v>394.9686550483849</v>
       </c>
       <c r="D65">
-        <v>953.7229850145645</v>
+        <v>954.7086550483849</v>
       </c>
       <c r="E65">
-        <v>187.6800000000001</v>
+        <v>197.34</v>
       </c>
       <c r="F65">
-        <v>608.58</v>
+        <v>618.24</v>
       </c>
       <c r="G65">
         <v>58.5</v>
@@ -6617,28 +6617,28 @@
         <v>119.775</v>
       </c>
       <c r="M65">
-        <v>39.009978</v>
+        <v>39.629184</v>
       </c>
       <c r="N65">
-        <v>80.76502199999997</v>
+        <v>80.14581599999997</v>
       </c>
       <c r="O65">
-        <v>19.38360527999999</v>
+        <v>19.23499583999999</v>
       </c>
       <c r="P65">
-        <v>61.38141671999998</v>
+        <v>60.91082015999997</v>
       </c>
       <c r="Q65">
-        <v>102.48141672</v>
+        <v>102.01082016</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1738779584096349</v>
+        <v>0.1770634768013291</v>
       </c>
       <c r="T65">
-        <v>1.763041306690357</v>
+        <v>1.806891166397023</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.070368304232316</v>
+        <v>3.022393799478686</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09492109164847848</v>
+        <v>0.09866945868539206</v>
       </c>
       <c r="C66">
-        <v>394.9686550483849</v>
+        <v>351.2862349392203</v>
       </c>
       <c r="D66">
-        <v>954.7086550483849</v>
+        <v>920.6862349392203</v>
       </c>
       <c r="E66">
-        <v>197.34</v>
+        <v>207</v>
       </c>
       <c r="F66">
-        <v>618.24</v>
+        <v>627.9</v>
       </c>
       <c r="G66">
         <v>58.5</v>
@@ -6699,45 +6699,45 @@
         <v>119.775</v>
       </c>
       <c r="M66">
-        <v>39.629184</v>
+        <v>45.14601</v>
       </c>
       <c r="N66">
-        <v>80.14581599999997</v>
+        <v>74.62898999999997</v>
       </c>
       <c r="O66">
-        <v>19.23499583999999</v>
+        <v>17.91095759999999</v>
       </c>
       <c r="P66">
-        <v>60.91082015999997</v>
+        <v>56.71803239999998</v>
       </c>
       <c r="Q66">
-        <v>102.01082016</v>
+        <v>97.81803239999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1770634768013291</v>
+        <v>0.1804310248154059</v>
       </c>
       <c r="T66">
-        <v>1.806891166397023</v>
+        <v>1.853246732372643</v>
       </c>
       <c r="U66">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V66">
         <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.022393799478686</v>
+        <v>2.653058376587432</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09866945868539206</v>
+        <v>0.09862390572230563</v>
       </c>
       <c r="C67">
-        <v>351.2862349392203</v>
+        <v>342.0251391681063</v>
       </c>
       <c r="D67">
-        <v>920.6862349392203</v>
+        <v>921.0851391681064</v>
       </c>
       <c r="E67">
-        <v>207</v>
+        <v>216.6600000000001</v>
       </c>
       <c r="F67">
-        <v>627.9</v>
+        <v>637.5600000000001</v>
       </c>
       <c r="G67">
         <v>58.5</v>
@@ -6781,28 +6781,28 @@
         <v>119.775</v>
       </c>
       <c r="M67">
-        <v>45.14601</v>
+        <v>45.84056400000001</v>
       </c>
       <c r="N67">
-        <v>74.62898999999997</v>
+        <v>73.93443599999998</v>
       </c>
       <c r="O67">
-        <v>17.91095759999999</v>
+        <v>17.74426463999999</v>
       </c>
       <c r="P67">
-        <v>56.71803239999998</v>
+        <v>56.19017135999998</v>
       </c>
       <c r="Q67">
-        <v>97.81803239999999</v>
+        <v>97.29017135999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1804310248154059</v>
+        <v>0.1839966638891342</v>
       </c>
       <c r="T67">
-        <v>1.853246732372643</v>
+        <v>1.902329096346828</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.653058376587432</v>
+        <v>2.612860522396713</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09862390572230563</v>
+        <v>0.09857835275921922</v>
       </c>
       <c r="C68">
-        <v>342.0251391681063</v>
+        <v>332.764389211997</v>
       </c>
       <c r="D68">
-        <v>921.0851391681064</v>
+        <v>921.484389211997</v>
       </c>
       <c r="E68">
-        <v>216.6600000000001</v>
+        <v>226.3200000000001</v>
       </c>
       <c r="F68">
-        <v>637.5600000000001</v>
+        <v>647.22</v>
       </c>
       <c r="G68">
         <v>58.5</v>
@@ -6863,28 +6863,28 @@
         <v>119.775</v>
       </c>
       <c r="M68">
-        <v>45.84056400000001</v>
+        <v>46.535118</v>
       </c>
       <c r="N68">
-        <v>73.93443599999998</v>
+        <v>73.23988199999997</v>
       </c>
       <c r="O68">
-        <v>17.74426463999999</v>
+        <v>17.57757167999999</v>
       </c>
       <c r="P68">
-        <v>56.19017135999998</v>
+        <v>55.66231031999997</v>
       </c>
       <c r="Q68">
-        <v>97.29017135999999</v>
+        <v>96.76231031999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1839966638891342</v>
+        <v>0.1877784023006643</v>
       </c>
       <c r="T68">
-        <v>1.902329096346828</v>
+        <v>1.954386149046721</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.612860522396713</v>
+        <v>2.573862604151986</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09857835275921922</v>
+        <v>0.09853279979613279</v>
       </c>
       <c r="C69">
-        <v>332.764389211997</v>
+        <v>323.5039855207748</v>
       </c>
       <c r="D69">
-        <v>921.484389211997</v>
+        <v>921.8839855207748</v>
       </c>
       <c r="E69">
-        <v>226.3200000000001</v>
+        <v>235.98</v>
       </c>
       <c r="F69">
-        <v>647.22</v>
+        <v>656.88</v>
       </c>
       <c r="G69">
         <v>58.5</v>
@@ -6945,28 +6945,28 @@
         <v>119.775</v>
       </c>
       <c r="M69">
-        <v>46.535118</v>
+        <v>47.229672</v>
       </c>
       <c r="N69">
-        <v>73.23988199999997</v>
+        <v>72.54532799999998</v>
       </c>
       <c r="O69">
-        <v>17.57757167999999</v>
+        <v>17.41087872</v>
       </c>
       <c r="P69">
-        <v>55.66231031999997</v>
+        <v>55.13444927999998</v>
       </c>
       <c r="Q69">
-        <v>96.76231031999998</v>
+        <v>96.23444927999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1877784023006643</v>
+        <v>0.191796499362915</v>
       </c>
       <c r="T69">
-        <v>1.954386149046721</v>
+        <v>2.009696767540357</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.573862604151986</v>
+        <v>2.536011683502693</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09853279979613279</v>
+        <v>0.1005324068330464</v>
       </c>
       <c r="C70">
-        <v>323.5039855207748</v>
+        <v>296.6233760043541</v>
       </c>
       <c r="D70">
-        <v>921.8839855207748</v>
+        <v>904.6633760043542</v>
       </c>
       <c r="E70">
-        <v>235.98</v>
+        <v>245.6400000000001</v>
       </c>
       <c r="F70">
-        <v>656.88</v>
+        <v>666.5400000000001</v>
       </c>
       <c r="G70">
         <v>58.5</v>
@@ -7027,45 +7027,45 @@
         <v>119.775</v>
       </c>
       <c r="M70">
-        <v>47.229672</v>
+        <v>50.52373200000001</v>
       </c>
       <c r="N70">
-        <v>72.54532799999998</v>
+        <v>69.25126799999997</v>
       </c>
       <c r="O70">
-        <v>17.41087872</v>
+        <v>16.62030431999999</v>
       </c>
       <c r="P70">
-        <v>55.13444927999998</v>
+        <v>52.63096367999998</v>
       </c>
       <c r="Q70">
-        <v>96.23444927999998</v>
+        <v>93.73096367999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.191796499362915</v>
+        <v>0.1960738284936979</v>
       </c>
       <c r="T70">
-        <v>2.009696767540357</v>
+        <v>2.068575813033583</v>
       </c>
       <c r="U70">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.24</v>
       </c>
       <c r="W70">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.536011683502693</v>
+        <v>2.37066810504022</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1005324068330464</v>
+        <v>0.1005164938699599</v>
       </c>
       <c r="C71">
-        <v>296.6233760043541</v>
+        <v>287.0978784623009</v>
       </c>
       <c r="D71">
-        <v>904.6633760043542</v>
+        <v>904.7978784623009</v>
       </c>
       <c r="E71">
-        <v>245.6400000000001</v>
+        <v>255.3000000000001</v>
       </c>
       <c r="F71">
-        <v>666.5400000000001</v>
+        <v>676.2</v>
       </c>
       <c r="G71">
         <v>58.5</v>
@@ -7109,28 +7109,28 @@
         <v>119.775</v>
       </c>
       <c r="M71">
-        <v>50.52373200000001</v>
+        <v>51.25596000000001</v>
       </c>
       <c r="N71">
-        <v>69.25126799999997</v>
+        <v>68.51903999999996</v>
       </c>
       <c r="O71">
-        <v>16.62030431999999</v>
+        <v>16.44456959999999</v>
       </c>
       <c r="P71">
-        <v>52.63096367999998</v>
+        <v>52.07447039999997</v>
       </c>
       <c r="Q71">
-        <v>93.73096367999997</v>
+        <v>93.17447039999996</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1960738284936979</v>
+        <v>0.2006363128998665</v>
       </c>
       <c r="T71">
-        <v>2.068575813033583</v>
+        <v>2.131380128226357</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.37066810504022</v>
+        <v>2.33680141782536</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1005164938699599</v>
+        <v>0.1005005809068735</v>
       </c>
       <c r="C72">
-        <v>287.0978784623009</v>
+        <v>277.5724209209856</v>
       </c>
       <c r="D72">
-        <v>904.7978784623009</v>
+        <v>904.9324209209857</v>
       </c>
       <c r="E72">
-        <v>255.3000000000001</v>
+        <v>264.9600000000002</v>
       </c>
       <c r="F72">
-        <v>676.2</v>
+        <v>685.8600000000001</v>
       </c>
       <c r="G72">
         <v>58.5</v>
@@ -7191,28 +7191,28 @@
         <v>119.775</v>
       </c>
       <c r="M72">
-        <v>51.25596000000001</v>
+        <v>51.98818800000002</v>
       </c>
       <c r="N72">
-        <v>68.51903999999996</v>
+        <v>67.78681199999997</v>
       </c>
       <c r="O72">
-        <v>16.44456959999999</v>
+        <v>16.26883487999999</v>
       </c>
       <c r="P72">
-        <v>52.07447039999997</v>
+        <v>51.51797711999998</v>
       </c>
       <c r="Q72">
-        <v>93.17447039999996</v>
+        <v>92.61797711999998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2006363128998665</v>
+        <v>0.2055134514030122</v>
       </c>
       <c r="T72">
-        <v>2.131380128226357</v>
+        <v>2.198515775501392</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.33680141782536</v>
+        <v>2.303888721799651</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1005005809068735</v>
+        <v>0.1004846679437871</v>
       </c>
       <c r="C73">
-        <v>277.5724209209857</v>
+        <v>268.047003398255</v>
       </c>
       <c r="D73">
-        <v>904.9324209209857</v>
+        <v>905.067003398255</v>
       </c>
       <c r="E73">
-        <v>264.96</v>
+        <v>274.62</v>
       </c>
       <c r="F73">
-        <v>685.86</v>
+        <v>695.52</v>
       </c>
       <c r="G73">
         <v>58.5</v>
@@ -7273,28 +7273,28 @@
         <v>119.775</v>
       </c>
       <c r="M73">
-        <v>51.98818800000001</v>
+        <v>52.720416</v>
       </c>
       <c r="N73">
-        <v>67.78681199999997</v>
+        <v>67.05458399999998</v>
       </c>
       <c r="O73">
-        <v>16.26883487999999</v>
+        <v>16.09310016</v>
       </c>
       <c r="P73">
-        <v>51.51797711999998</v>
+        <v>50.96148383999999</v>
       </c>
       <c r="Q73">
-        <v>92.61797711999998</v>
+        <v>92.06148383999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2055134514030121</v>
+        <v>0.2107389569420967</v>
       </c>
       <c r="T73">
-        <v>2.198515775501391</v>
+        <v>2.270446826153214</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.303888721799651</v>
+        <v>2.271890267330212</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1004846679437871</v>
+        <v>0.1004687549807007</v>
       </c>
       <c r="C74">
-        <v>268.047003398255</v>
+        <v>258.5216259119668</v>
       </c>
       <c r="D74">
-        <v>905.067003398255</v>
+        <v>905.2016259119667</v>
       </c>
       <c r="E74">
-        <v>274.62</v>
+        <v>284.28</v>
       </c>
       <c r="F74">
-        <v>695.52</v>
+        <v>705.1799999999999</v>
       </c>
       <c r="G74">
         <v>58.5</v>
@@ -7355,28 +7355,28 @@
         <v>119.775</v>
       </c>
       <c r="M74">
-        <v>52.720416</v>
+        <v>53.452644</v>
       </c>
       <c r="N74">
-        <v>67.05458399999998</v>
+        <v>66.32235599999998</v>
       </c>
       <c r="O74">
-        <v>16.09310016</v>
+        <v>15.91736544</v>
       </c>
       <c r="P74">
-        <v>50.96148383999999</v>
+        <v>50.40499055999999</v>
       </c>
       <c r="Q74">
-        <v>92.06148383999999</v>
+        <v>91.50499055999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2107389569420967</v>
+        <v>0.216351536965558</v>
       </c>
       <c r="T74">
-        <v>2.270446826153214</v>
+        <v>2.347706102779245</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.271890267330212</v>
+        <v>2.240768482846236</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1004687549807007</v>
+        <v>0.1004528420176142</v>
       </c>
       <c r="C75">
-        <v>258.5216259119668</v>
+        <v>248.9962884799888</v>
       </c>
       <c r="D75">
-        <v>905.2016259119667</v>
+        <v>905.3362884799889</v>
       </c>
       <c r="E75">
-        <v>284.28</v>
+        <v>293.9400000000001</v>
       </c>
       <c r="F75">
-        <v>705.1799999999999</v>
+        <v>714.84</v>
       </c>
       <c r="G75">
         <v>58.5</v>
@@ -7437,28 +7437,28 @@
         <v>119.775</v>
       </c>
       <c r="M75">
-        <v>53.452644</v>
+        <v>54.18487200000001</v>
       </c>
       <c r="N75">
-        <v>66.32235599999998</v>
+        <v>65.59012799999996</v>
       </c>
       <c r="O75">
-        <v>15.91736544</v>
+        <v>15.74163071999999</v>
       </c>
       <c r="P75">
-        <v>50.40499055999999</v>
+        <v>49.84849727999998</v>
       </c>
       <c r="Q75">
-        <v>91.50499055999998</v>
+        <v>90.94849727999997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.216351536965558</v>
+        <v>0.2223958539139009</v>
       </c>
       <c r="T75">
-        <v>2.347706102779245</v>
+        <v>2.430908400684202</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.240768482846236</v>
+        <v>2.210487827672638</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1004528420176142</v>
+        <v>0.1004369290545278</v>
       </c>
       <c r="C76">
-        <v>248.9962884799888</v>
+        <v>239.4709911201996</v>
       </c>
       <c r="D76">
-        <v>905.3362884799889</v>
+        <v>905.4709911201996</v>
       </c>
       <c r="E76">
-        <v>293.9400000000001</v>
+        <v>303.6</v>
       </c>
       <c r="F76">
-        <v>714.84</v>
+        <v>724.5</v>
       </c>
       <c r="G76">
         <v>58.5</v>
@@ -7519,28 +7519,28 @@
         <v>119.775</v>
       </c>
       <c r="M76">
-        <v>54.18487200000001</v>
+        <v>54.9171</v>
       </c>
       <c r="N76">
-        <v>65.59012799999996</v>
+        <v>64.85789999999997</v>
       </c>
       <c r="O76">
-        <v>15.74163071999999</v>
+        <v>15.56589599999999</v>
       </c>
       <c r="P76">
-        <v>49.84849727999998</v>
+        <v>49.29200399999998</v>
       </c>
       <c r="Q76">
-        <v>90.94849727999997</v>
+        <v>90.39200399999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2223958539139009</v>
+        <v>0.2289237162181113</v>
       </c>
       <c r="T76">
-        <v>2.430908400684202</v>
+        <v>2.520766882421556</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.210487827672638</v>
+        <v>2.181014656637003</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1004369290545278</v>
+        <v>0.1004210160914414</v>
       </c>
       <c r="C77">
-        <v>239.4709911201996</v>
+        <v>229.9457338504891</v>
       </c>
       <c r="D77">
-        <v>905.4709911201996</v>
+        <v>905.6057338504891</v>
       </c>
       <c r="E77">
-        <v>303.6</v>
+        <v>313.26</v>
       </c>
       <c r="F77">
-        <v>724.5</v>
+        <v>734.16</v>
       </c>
       <c r="G77">
         <v>58.5</v>
@@ -7601,28 +7601,28 @@
         <v>119.775</v>
       </c>
       <c r="M77">
-        <v>54.9171</v>
+        <v>55.649328</v>
       </c>
       <c r="N77">
-        <v>64.85789999999997</v>
+        <v>64.12567199999998</v>
       </c>
       <c r="O77">
-        <v>15.56589599999999</v>
+        <v>15.39016127999999</v>
       </c>
       <c r="P77">
-        <v>49.29200399999998</v>
+        <v>48.73551071999999</v>
       </c>
       <c r="Q77">
-        <v>90.39200399999999</v>
+        <v>89.83551071999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2289237162181113</v>
+        <v>0.2359955670476725</v>
       </c>
       <c r="T77">
-        <v>2.520766882421556</v>
+        <v>2.618113570970356</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.181014656637003</v>
+        <v>2.152317095365464</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1004210160914414</v>
+        <v>0.100405103128355</v>
       </c>
       <c r="C78">
-        <v>229.9457338504891</v>
+        <v>220.4205166887568</v>
       </c>
       <c r="D78">
-        <v>905.6057338504891</v>
+        <v>905.7405166887569</v>
       </c>
       <c r="E78">
-        <v>313.26</v>
+        <v>322.9200000000001</v>
       </c>
       <c r="F78">
-        <v>734.16</v>
+        <v>743.8200000000001</v>
       </c>
       <c r="G78">
         <v>58.5</v>
@@ -7683,28 +7683,28 @@
         <v>119.775</v>
       </c>
       <c r="M78">
-        <v>55.649328</v>
+        <v>56.38155600000001</v>
       </c>
       <c r="N78">
-        <v>64.12567199999998</v>
+        <v>63.39344399999997</v>
       </c>
       <c r="O78">
-        <v>15.39016127999999</v>
+        <v>15.21442655999999</v>
       </c>
       <c r="P78">
-        <v>48.73551071999999</v>
+        <v>48.17901743999997</v>
       </c>
       <c r="Q78">
-        <v>89.83551071999999</v>
+        <v>89.27901743999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2359955670476725</v>
+        <v>0.2436823614276303</v>
       </c>
       <c r="T78">
-        <v>2.618113570970356</v>
+        <v>2.723925188958182</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.152317095365464</v>
+        <v>2.124364925295782</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.100405103128355</v>
+        <v>0.1003891901652686</v>
       </c>
       <c r="C79">
-        <v>220.4205166887568</v>
+        <v>210.8953396529139</v>
       </c>
       <c r="D79">
-        <v>905.7405166887569</v>
+        <v>905.8753396529139</v>
       </c>
       <c r="E79">
-        <v>322.9200000000001</v>
+        <v>332.58</v>
       </c>
       <c r="F79">
-        <v>743.8200000000001</v>
+        <v>753.48</v>
       </c>
       <c r="G79">
         <v>58.5</v>
@@ -7765,28 +7765,28 @@
         <v>119.775</v>
       </c>
       <c r="M79">
-        <v>56.38155600000001</v>
+        <v>57.113784</v>
       </c>
       <c r="N79">
-        <v>63.39344399999997</v>
+        <v>62.66121599999997</v>
       </c>
       <c r="O79">
-        <v>15.21442655999999</v>
+        <v>15.03869183999999</v>
       </c>
       <c r="P79">
-        <v>48.17901743999997</v>
+        <v>47.62252415999998</v>
       </c>
       <c r="Q79">
-        <v>89.27901743999998</v>
+        <v>88.72252415999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2436823614276303</v>
+        <v>0.2520679552966753</v>
       </c>
       <c r="T79">
-        <v>2.723925188958182</v>
+        <v>2.839356044944902</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.124364925295782</v>
+        <v>2.09712947753558</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1003891901652686</v>
+        <v>0.1003732772021821</v>
       </c>
       <c r="C80">
-        <v>210.8953396529139</v>
+        <v>201.3702027608814</v>
       </c>
       <c r="D80">
-        <v>905.8753396529139</v>
+        <v>906.0102027608814</v>
       </c>
       <c r="E80">
-        <v>332.58</v>
+        <v>342.24</v>
       </c>
       <c r="F80">
-        <v>753.48</v>
+        <v>763.14</v>
       </c>
       <c r="G80">
         <v>58.5</v>
@@ -7847,28 +7847,28 @@
         <v>119.775</v>
       </c>
       <c r="M80">
-        <v>57.113784</v>
+        <v>57.846012</v>
       </c>
       <c r="N80">
-        <v>62.66121599999997</v>
+        <v>61.92898799999998</v>
       </c>
       <c r="O80">
-        <v>15.03869183999999</v>
+        <v>14.86295711999999</v>
       </c>
       <c r="P80">
-        <v>47.62252415999998</v>
+        <v>47.06603087999999</v>
       </c>
       <c r="Q80">
-        <v>88.72252415999998</v>
+        <v>88.16603087999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2520679552966753</v>
+        <v>0.2612521771532483</v>
       </c>
       <c r="T80">
-        <v>2.839356044944902</v>
+        <v>2.965780315787499</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.09712947753558</v>
+        <v>2.070583534781965</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1003732772021821</v>
+        <v>0.1003573642390957</v>
       </c>
       <c r="C81">
-        <v>201.3702027608814</v>
+        <v>191.8451060305913</v>
       </c>
       <c r="D81">
-        <v>906.0102027608814</v>
+        <v>906.1451060305914</v>
       </c>
       <c r="E81">
-        <v>342.24</v>
+        <v>351.9000000000001</v>
       </c>
       <c r="F81">
-        <v>763.14</v>
+        <v>772.8000000000001</v>
       </c>
       <c r="G81">
         <v>58.5</v>
@@ -7929,28 +7929,28 @@
         <v>119.775</v>
       </c>
       <c r="M81">
-        <v>57.846012</v>
+        <v>58.57824000000001</v>
       </c>
       <c r="N81">
-        <v>61.92898799999998</v>
+        <v>61.19675999999997</v>
       </c>
       <c r="O81">
-        <v>14.86295711999999</v>
+        <v>14.68722239999999</v>
       </c>
       <c r="P81">
-        <v>47.06603087999999</v>
+        <v>46.50953759999997</v>
       </c>
       <c r="Q81">
-        <v>88.16603087999999</v>
+        <v>87.60953759999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2612521771532483</v>
+        <v>0.2713548211954786</v>
       </c>
       <c r="T81">
-        <v>2.965780315787499</v>
+        <v>3.104847013714357</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.070583534781965</v>
+        <v>2.04470124059719</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1003573642390957</v>
+        <v>0.1003414512760093</v>
       </c>
       <c r="C82">
-        <v>191.8451060305913</v>
+        <v>182.3200494799866</v>
       </c>
       <c r="D82">
-        <v>906.1451060305914</v>
+        <v>906.2800494799866</v>
       </c>
       <c r="E82">
-        <v>351.9000000000001</v>
+        <v>361.5600000000001</v>
       </c>
       <c r="F82">
-        <v>772.8000000000001</v>
+        <v>782.46</v>
       </c>
       <c r="G82">
         <v>58.5</v>
@@ -8011,28 +8011,28 @@
         <v>119.775</v>
       </c>
       <c r="M82">
-        <v>58.57824000000001</v>
+        <v>59.31046800000001</v>
       </c>
       <c r="N82">
-        <v>61.19675999999997</v>
+        <v>60.46453199999997</v>
       </c>
       <c r="O82">
-        <v>14.68722239999999</v>
+        <v>14.51148767999999</v>
       </c>
       <c r="P82">
-        <v>46.50953759999997</v>
+        <v>45.95304431999998</v>
       </c>
       <c r="Q82">
-        <v>87.60953759999998</v>
+        <v>87.05304431999997</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2713548211954786</v>
+        <v>0.2825209014526805</v>
       </c>
       <c r="T82">
-        <v>3.104847013714357</v>
+        <v>3.258552311422988</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.04470124059719</v>
+        <v>2.019458015404632</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1003414512760093</v>
+        <v>0.1091749783129229</v>
       </c>
       <c r="C83">
-        <v>182.3200494799866</v>
+        <v>103.4603376106033</v>
       </c>
       <c r="D83">
-        <v>906.2800494799866</v>
+        <v>837.0803376106034</v>
       </c>
       <c r="E83">
-        <v>361.5600000000001</v>
+        <v>371.22</v>
       </c>
       <c r="F83">
-        <v>782.46</v>
+        <v>792.12</v>
       </c>
       <c r="G83">
         <v>58.5</v>
@@ -8093,45 +8093,45 @@
         <v>119.775</v>
       </c>
       <c r="M83">
-        <v>59.31046800000001</v>
+        <v>71.2908</v>
       </c>
       <c r="N83">
-        <v>60.46453199999997</v>
+        <v>48.48419999999997</v>
       </c>
       <c r="O83">
-        <v>14.51148767999999</v>
+        <v>11.63620799999999</v>
       </c>
       <c r="P83">
-        <v>45.95304431999998</v>
+        <v>36.84799199999998</v>
       </c>
       <c r="Q83">
-        <v>87.05304431999997</v>
+        <v>77.94799199999997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2825209014526805</v>
+        <v>0.2949276572940159</v>
       </c>
       <c r="T83">
-        <v>3.258552311422988</v>
+        <v>3.42933597554369</v>
       </c>
       <c r="U83">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V83">
         <v>0.24</v>
       </c>
       <c r="W83">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.019458015404632</v>
+        <v>1.680090558669562</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1091749783129229</v>
+        <v>0.1092669853498364</v>
       </c>
       <c r="C84">
-        <v>103.4603376106033</v>
+        <v>93.13514004107731</v>
       </c>
       <c r="D84">
-        <v>837.0803376106034</v>
+        <v>836.4151400410774</v>
       </c>
       <c r="E84">
-        <v>371.22</v>
+        <v>380.8800000000001</v>
       </c>
       <c r="F84">
-        <v>792.12</v>
+        <v>801.7800000000001</v>
       </c>
       <c r="G84">
         <v>58.5</v>
@@ -8175,28 +8175,28 @@
         <v>119.775</v>
       </c>
       <c r="M84">
-        <v>71.2908</v>
+        <v>72.1602</v>
       </c>
       <c r="N84">
-        <v>48.48419999999997</v>
+        <v>47.61479999999997</v>
       </c>
       <c r="O84">
-        <v>11.63620799999999</v>
+        <v>11.42755199999999</v>
       </c>
       <c r="P84">
-        <v>36.84799199999998</v>
+        <v>36.18724799999998</v>
       </c>
       <c r="Q84">
-        <v>77.94799199999997</v>
+        <v>77.28724799999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2949276572940159</v>
+        <v>0.3087940314696263</v>
       </c>
       <c r="T84">
-        <v>3.42933597554369</v>
+        <v>3.620211835443298</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.680090558669562</v>
+        <v>1.659848503745832</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1092669853498364</v>
+        <v>0.10935899238675</v>
       </c>
       <c r="C85">
-        <v>93.13514004107731</v>
+        <v>82.81099884914602</v>
       </c>
       <c r="D85">
-        <v>836.4151400410774</v>
+        <v>835.7509988491461</v>
       </c>
       <c r="E85">
-        <v>380.8800000000001</v>
+        <v>390.5400000000001</v>
       </c>
       <c r="F85">
-        <v>801.7800000000001</v>
+        <v>811.4400000000001</v>
       </c>
       <c r="G85">
         <v>58.5</v>
@@ -8257,28 +8257,28 @@
         <v>119.775</v>
       </c>
       <c r="M85">
-        <v>72.1602</v>
+        <v>73.0296</v>
       </c>
       <c r="N85">
-        <v>47.61479999999997</v>
+        <v>46.74539999999998</v>
       </c>
       <c r="O85">
-        <v>11.42755199999999</v>
+        <v>11.21889599999999</v>
       </c>
       <c r="P85">
-        <v>36.18724799999998</v>
+        <v>35.52650399999998</v>
       </c>
       <c r="Q85">
-        <v>77.28724799999998</v>
+        <v>76.62650399999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3087940314696263</v>
+        <v>0.3243937024171877</v>
       </c>
       <c r="T85">
-        <v>3.620211835443298</v>
+        <v>3.834947177830358</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.659848503745832</v>
+        <v>1.640088402510762</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.10935899238675</v>
+        <v>0.1094509994236636</v>
       </c>
       <c r="C86">
-        <v>82.81099884914602</v>
+        <v>72.48791152040917</v>
       </c>
       <c r="D86">
-        <v>835.750998849146</v>
+        <v>835.0879115204092</v>
       </c>
       <c r="E86">
-        <v>390.54</v>
+        <v>400.2</v>
       </c>
       <c r="F86">
-        <v>811.4399999999999</v>
+        <v>821.1</v>
       </c>
       <c r="G86">
         <v>58.5</v>
@@ -8339,28 +8339,28 @@
         <v>119.775</v>
       </c>
       <c r="M86">
-        <v>73.02959999999999</v>
+        <v>73.899</v>
       </c>
       <c r="N86">
-        <v>46.74539999999999</v>
+        <v>45.87599999999998</v>
       </c>
       <c r="O86">
-        <v>11.218896</v>
+        <v>11.01023999999999</v>
       </c>
       <c r="P86">
-        <v>35.52650399999999</v>
+        <v>34.86575999999998</v>
       </c>
       <c r="Q86">
-        <v>76.62650399999998</v>
+        <v>75.96575999999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3243937024171876</v>
+        <v>0.3420733294910906</v>
       </c>
       <c r="T86">
-        <v>3.834947177830355</v>
+        <v>4.078313899202356</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.640088402510763</v>
+        <v>1.620793244834165</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1094509994236636</v>
+        <v>0.1095430064605772</v>
       </c>
       <c r="C87">
-        <v>72.48791152040917</v>
+        <v>62.16587554844125</v>
       </c>
       <c r="D87">
-        <v>835.0879115204092</v>
+        <v>834.4258755484412</v>
       </c>
       <c r="E87">
-        <v>400.2</v>
+        <v>409.86</v>
       </c>
       <c r="F87">
-        <v>821.1</v>
+        <v>830.76</v>
       </c>
       <c r="G87">
         <v>58.5</v>
@@ -8421,28 +8421,28 @@
         <v>119.775</v>
       </c>
       <c r="M87">
-        <v>73.899</v>
+        <v>74.7684</v>
       </c>
       <c r="N87">
-        <v>45.87599999999998</v>
+        <v>45.00659999999998</v>
       </c>
       <c r="O87">
-        <v>11.01023999999999</v>
+        <v>10.80158399999999</v>
       </c>
       <c r="P87">
-        <v>34.86575999999998</v>
+        <v>34.20501599999999</v>
       </c>
       <c r="Q87">
-        <v>75.96575999999999</v>
+        <v>75.30501599999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3420733294910906</v>
+        <v>0.3622786175755512</v>
       </c>
       <c r="T87">
-        <v>4.078313899202356</v>
+        <v>4.35644729505607</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.620793244834165</v>
+        <v>1.601946811754698</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1095430064605772</v>
+        <v>0.1096350134974907</v>
       </c>
       <c r="C88">
-        <v>62.16587554844125</v>
+        <v>51.8448884347581</v>
       </c>
       <c r="D88">
-        <v>834.4258755484412</v>
+        <v>833.7648884347581</v>
       </c>
       <c r="E88">
-        <v>409.86</v>
+        <v>419.52</v>
       </c>
       <c r="F88">
-        <v>830.76</v>
+        <v>840.42</v>
       </c>
       <c r="G88">
         <v>58.5</v>
@@ -8503,28 +8503,28 @@
         <v>119.775</v>
       </c>
       <c r="M88">
-        <v>74.7684</v>
+        <v>75.6378</v>
       </c>
       <c r="N88">
-        <v>45.00659999999998</v>
+        <v>44.13719999999998</v>
       </c>
       <c r="O88">
-        <v>10.80158399999999</v>
+        <v>10.592928</v>
       </c>
       <c r="P88">
-        <v>34.20501599999999</v>
+        <v>33.54427199999999</v>
       </c>
       <c r="Q88">
-        <v>75.30501599999999</v>
+        <v>74.64427199999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3622786175755512</v>
+        <v>0.3855924115191596</v>
       </c>
       <c r="T88">
-        <v>4.35644729505607</v>
+        <v>4.677370444118047</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.601946811754698</v>
+        <v>1.583533630010391</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1096350134974907</v>
+        <v>0.1097270205344043</v>
       </c>
       <c r="C89">
-        <v>51.8448884347581</v>
+        <v>41.52494768878569</v>
       </c>
       <c r="D89">
-        <v>833.7648884347581</v>
+        <v>833.1049476887857</v>
       </c>
       <c r="E89">
-        <v>419.52</v>
+        <v>429.1800000000001</v>
       </c>
       <c r="F89">
-        <v>840.42</v>
+        <v>850.08</v>
       </c>
       <c r="G89">
         <v>58.5</v>
@@ -8585,28 +8585,28 @@
         <v>119.775</v>
       </c>
       <c r="M89">
-        <v>75.6378</v>
+        <v>76.5072</v>
       </c>
       <c r="N89">
-        <v>44.13719999999998</v>
+        <v>43.26779999999998</v>
       </c>
       <c r="O89">
-        <v>10.592928</v>
+        <v>10.38427199999999</v>
       </c>
       <c r="P89">
-        <v>33.54427199999999</v>
+        <v>32.88352799999998</v>
       </c>
       <c r="Q89">
-        <v>74.64427199999999</v>
+        <v>73.98352799999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3855924115191596</v>
+        <v>0.4127918377867028</v>
       </c>
       <c r="T89">
-        <v>4.677370444118047</v>
+        <v>5.051780784690355</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.583533630010391</v>
+        <v>1.565538929669364</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1097270205344043</v>
+        <v>0.1098190275713179</v>
       </c>
       <c r="C90">
-        <v>41.52494768878569</v>
+        <v>31.20605082782981</v>
       </c>
       <c r="D90">
-        <v>833.1049476887857</v>
+        <v>832.4460508278298</v>
       </c>
       <c r="E90">
-        <v>429.1800000000001</v>
+        <v>438.84</v>
       </c>
       <c r="F90">
-        <v>850.08</v>
+        <v>859.74</v>
       </c>
       <c r="G90">
         <v>58.5</v>
@@ -8667,28 +8667,28 @@
         <v>119.775</v>
       </c>
       <c r="M90">
-        <v>76.5072</v>
+        <v>77.3766</v>
       </c>
       <c r="N90">
-        <v>43.26779999999998</v>
+        <v>42.39839999999998</v>
       </c>
       <c r="O90">
-        <v>10.38427199999999</v>
+        <v>10.17561599999999</v>
       </c>
       <c r="P90">
-        <v>32.88352799999998</v>
+        <v>32.22278399999999</v>
       </c>
       <c r="Q90">
-        <v>73.98352799999998</v>
+        <v>73.32278399999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4127918377867028</v>
+        <v>0.4449366142847082</v>
       </c>
       <c r="T90">
-        <v>5.051780784690355</v>
+        <v>5.494265732639446</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.565538929669364</v>
+        <v>1.5479486046169</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1098190275713179</v>
+        <v>0.1099110346082315</v>
       </c>
       <c r="C91">
-        <v>31.20605082782981</v>
+        <v>20.8881953770433</v>
       </c>
       <c r="D91">
-        <v>832.4460508278298</v>
+        <v>831.7881953770433</v>
       </c>
       <c r="E91">
-        <v>438.84</v>
+        <v>448.5</v>
       </c>
       <c r="F91">
-        <v>859.74</v>
+        <v>869.4</v>
       </c>
       <c r="G91">
         <v>58.5</v>
@@ -8749,28 +8749,28 @@
         <v>119.775</v>
       </c>
       <c r="M91">
-        <v>77.3766</v>
+        <v>78.246</v>
       </c>
       <c r="N91">
-        <v>42.39839999999998</v>
+        <v>41.52899999999998</v>
       </c>
       <c r="O91">
-        <v>10.17561599999999</v>
+        <v>9.966959999999995</v>
       </c>
       <c r="P91">
-        <v>32.22278399999999</v>
+        <v>31.56203999999999</v>
       </c>
       <c r="Q91">
-        <v>73.32278399999998</v>
+        <v>72.66203999999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4449366142847082</v>
+        <v>0.4835103460823149</v>
       </c>
       <c r="T91">
-        <v>5.494265732639446</v>
+        <v>6.025247670178356</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.5479486046169</v>
+        <v>1.530749175676712</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1099110346082315</v>
+        <v>0.110003041645145</v>
       </c>
       <c r="C92">
-        <v>20.8881953770433</v>
+        <v>10.57137886939688</v>
       </c>
       <c r="D92">
-        <v>831.7881953770433</v>
+        <v>831.1313788693969</v>
       </c>
       <c r="E92">
-        <v>448.5</v>
+        <v>458.1600000000001</v>
       </c>
       <c r="F92">
-        <v>869.4</v>
+        <v>879.0600000000001</v>
       </c>
       <c r="G92">
         <v>58.5</v>
@@ -8831,28 +8831,28 @@
         <v>119.775</v>
       </c>
       <c r="M92">
-        <v>78.246</v>
+        <v>79.11540000000001</v>
       </c>
       <c r="N92">
-        <v>41.52899999999998</v>
+        <v>40.65959999999997</v>
       </c>
       <c r="O92">
-        <v>9.966959999999995</v>
+        <v>9.758303999999992</v>
       </c>
       <c r="P92">
-        <v>31.56203999999999</v>
+        <v>30.90129599999998</v>
       </c>
       <c r="Q92">
-        <v>72.66203999999999</v>
+        <v>72.00129599999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4835103460823149</v>
+        <v>0.5306560182793896</v>
       </c>
       <c r="T92">
-        <v>6.025247670178356</v>
+        <v>6.674225593837022</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.530749175676712</v>
+        <v>1.513927756163781</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.110003041645145</v>
+        <v>0.1534752810158456</v>
       </c>
       <c r="C93">
-        <v>10.57137886939688</v>
+        <v>-224.9232804726083</v>
       </c>
       <c r="D93">
-        <v>831.1313788693969</v>
+        <v>605.2967195273917</v>
       </c>
       <c r="E93">
-        <v>458.1600000000001</v>
+        <v>467.8200000000001</v>
       </c>
       <c r="F93">
-        <v>879.0600000000001</v>
+        <v>888.72</v>
       </c>
       <c r="G93">
         <v>58.5</v>
@@ -8913,45 +8913,45 @@
         <v>119.775</v>
       </c>
       <c r="M93">
-        <v>79.11540000000001</v>
+        <v>130.464096</v>
       </c>
       <c r="N93">
-        <v>40.65959999999997</v>
+        <v>-10.68909600000003</v>
       </c>
       <c r="O93">
-        <v>9.758303999999992</v>
+        <v>-2.565383040000008</v>
       </c>
       <c r="P93">
-        <v>30.90129599999998</v>
+        <v>-8.123712960000027</v>
       </c>
       <c r="Q93">
-        <v>72.00129599999998</v>
+        <v>32.97628703999997</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5306560182793896</v>
+        <v>0.6022130623875108</v>
       </c>
       <c r="T93">
-        <v>6.674225593837022</v>
+        <v>7.659235240413268</v>
       </c>
       <c r="U93">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.24</v>
+        <v>0.2203364824602777</v>
       </c>
       <c r="W93">
-        <v>0.0684</v>
+        <v>0.1144546043748312</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.513927756163781</v>
+        <v>0.9180686769178239</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1534752810158456</v>
+        <v>0.1544852810158456</v>
       </c>
       <c r="C94">
-        <v>-224.9232804726083</v>
+        <v>-238.380498628197</v>
       </c>
       <c r="D94">
-        <v>605.2967195273917</v>
+        <v>601.499501371803</v>
       </c>
       <c r="E94">
-        <v>467.8200000000001</v>
+        <v>477.48</v>
       </c>
       <c r="F94">
-        <v>888.72</v>
+        <v>898.38</v>
       </c>
       <c r="G94">
         <v>58.5</v>
@@ -8995,37 +8995,37 @@
         <v>119.775</v>
       </c>
       <c r="M94">
-        <v>130.464096</v>
+        <v>131.882184</v>
       </c>
       <c r="N94">
-        <v>-10.68909600000003</v>
+        <v>-12.10718400000005</v>
       </c>
       <c r="O94">
-        <v>-2.565383040000008</v>
+        <v>-2.905724160000011</v>
       </c>
       <c r="P94">
-        <v>-8.123712960000027</v>
+        <v>-9.201459840000036</v>
       </c>
       <c r="Q94">
-        <v>32.97628703999997</v>
+        <v>31.89854015999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6022130623875108</v>
+        <v>0.6817006427285837</v>
       </c>
       <c r="T94">
-        <v>7.659235240413268</v>
+        <v>8.753411703329448</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2203364824602777</v>
+        <v>0.2179672729714575</v>
       </c>
       <c r="W94">
-        <v>0.1144546043748312</v>
+        <v>0.11480240432779</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9180686769178239</v>
+        <v>0.9081969707144064</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1544852810158456</v>
+        <v>0.1554952810158456</v>
       </c>
       <c r="C95">
-        <v>-238.380498628197</v>
+        <v>-251.7903714899678</v>
       </c>
       <c r="D95">
-        <v>601.499501371803</v>
+        <v>597.7496285100323</v>
       </c>
       <c r="E95">
-        <v>477.48</v>
+        <v>487.1400000000001</v>
       </c>
       <c r="F95">
-        <v>898.38</v>
+        <v>908.0400000000001</v>
       </c>
       <c r="G95">
         <v>58.5</v>
@@ -9077,37 +9077,37 @@
         <v>119.775</v>
       </c>
       <c r="M95">
-        <v>131.882184</v>
+        <v>133.300272</v>
       </c>
       <c r="N95">
-        <v>-12.10718400000005</v>
+        <v>-13.52527200000006</v>
       </c>
       <c r="O95">
-        <v>-2.905724160000011</v>
+        <v>-3.246065280000014</v>
       </c>
       <c r="P95">
-        <v>-9.201459840000036</v>
+        <v>-10.27920672000004</v>
       </c>
       <c r="Q95">
-        <v>31.89854015999997</v>
+        <v>30.82079327999996</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6817006427285837</v>
+        <v>0.7876840831833479</v>
       </c>
       <c r="T95">
-        <v>8.753411703329448</v>
+        <v>10.21231365388436</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2179672729714575</v>
+        <v>0.2156484721951654</v>
       </c>
       <c r="W95">
-        <v>0.11480240432779</v>
+        <v>0.1151428042817497</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9081969707144064</v>
+        <v>0.8985353008131892</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1554952810158456</v>
+        <v>0.1565052810158456</v>
       </c>
       <c r="C96">
-        <v>-251.7903714899678</v>
+        <v>-265.1537790530432</v>
       </c>
       <c r="D96">
-        <v>597.7496285100323</v>
+        <v>594.0462209469569</v>
       </c>
       <c r="E96">
-        <v>487.1400000000001</v>
+        <v>496.8000000000001</v>
       </c>
       <c r="F96">
-        <v>908.0400000000001</v>
+        <v>917.7</v>
       </c>
       <c r="G96">
         <v>58.5</v>
@@ -9159,37 +9159,37 @@
         <v>119.775</v>
       </c>
       <c r="M96">
-        <v>133.300272</v>
+        <v>134.71836</v>
       </c>
       <c r="N96">
-        <v>-13.52527200000006</v>
+        <v>-14.94336000000004</v>
       </c>
       <c r="O96">
-        <v>-3.246065280000014</v>
+        <v>-3.58640640000001</v>
       </c>
       <c r="P96">
-        <v>-10.27920672000004</v>
+        <v>-11.35695360000003</v>
       </c>
       <c r="Q96">
-        <v>30.82079327999996</v>
+        <v>29.74304639999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7876840831833479</v>
+        <v>0.9360608998200179</v>
       </c>
       <c r="T96">
-        <v>10.21231365388436</v>
+        <v>12.25477638466124</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2156484721951654</v>
+        <v>0.2133784882773216</v>
       </c>
       <c r="W96">
-        <v>0.1151428042817497</v>
+        <v>0.1154760379208892</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8985353008131892</v>
+        <v>0.88907703448884</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1565052810158456</v>
+        <v>0.1575152810158456</v>
       </c>
       <c r="C97">
-        <v>-265.1537790530432</v>
+        <v>-278.4715796384975</v>
       </c>
       <c r="D97">
-        <v>594.0462209469569</v>
+        <v>590.3884203615027</v>
       </c>
       <c r="E97">
-        <v>496.8000000000001</v>
+        <v>506.4600000000002</v>
       </c>
       <c r="F97">
-        <v>917.7</v>
+        <v>927.3600000000001</v>
       </c>
       <c r="G97">
         <v>58.5</v>
@@ -9241,37 +9241,37 @@
         <v>119.775</v>
       </c>
       <c r="M97">
-        <v>134.71836</v>
+        <v>136.136448</v>
       </c>
       <c r="N97">
-        <v>-14.94336000000004</v>
+        <v>-16.36144800000005</v>
       </c>
       <c r="O97">
-        <v>-3.58640640000001</v>
+        <v>-3.926747520000013</v>
       </c>
       <c r="P97">
-        <v>-11.35695360000003</v>
+        <v>-12.43470048000004</v>
       </c>
       <c r="Q97">
-        <v>29.74304639999997</v>
+        <v>28.66529951999996</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9360608998200179</v>
+        <v>1.158626124775023</v>
       </c>
       <c r="T97">
-        <v>12.25477638466124</v>
+        <v>15.31847048082656</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2133784882773216</v>
+        <v>0.2111557956910995</v>
       </c>
       <c r="W97">
-        <v>0.1154760379208892</v>
+        <v>0.1158023291925466</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.88907703448884</v>
+        <v>0.8798158153795812</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1575152810158456</v>
+        <v>0.1585252810158456</v>
       </c>
       <c r="C98">
-        <v>-278.4715796384974</v>
+        <v>-291.7446105565542</v>
       </c>
       <c r="D98">
-        <v>590.3884203615027</v>
+        <v>586.7753894434458</v>
       </c>
       <c r="E98">
-        <v>506.46</v>
+        <v>516.12</v>
       </c>
       <c r="F98">
-        <v>927.36</v>
+        <v>937.02</v>
       </c>
       <c r="G98">
         <v>58.5</v>
@@ -9323,37 +9323,37 @@
         <v>119.775</v>
       </c>
       <c r="M98">
-        <v>136.136448</v>
+        <v>137.554536</v>
       </c>
       <c r="N98">
-        <v>-16.36144800000002</v>
+        <v>-17.77953600000004</v>
       </c>
       <c r="O98">
-        <v>-3.926747520000005</v>
+        <v>-4.267088640000009</v>
       </c>
       <c r="P98">
-        <v>-12.43470048000002</v>
+        <v>-13.51244736000003</v>
       </c>
       <c r="Q98">
-        <v>28.66529951999998</v>
+        <v>27.58755263999997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.15862612477502</v>
+        <v>1.529568166366693</v>
       </c>
       <c r="T98">
-        <v>15.31847048082651</v>
+        <v>20.42462730776868</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2111557956910995</v>
+        <v>0.2089789318179954</v>
       </c>
       <c r="W98">
-        <v>0.1158023291925466</v>
+        <v>0.1161218928091183</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8798158153795813</v>
+        <v>0.8707455492416474</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1585252810158456</v>
+        <v>0.1595352810158456</v>
       </c>
       <c r="C99">
-        <v>-291.7446105565542</v>
+        <v>-304.9736887455845</v>
       </c>
       <c r="D99">
-        <v>586.7753894434458</v>
+        <v>583.2063112544155</v>
       </c>
       <c r="E99">
-        <v>516.12</v>
+        <v>525.78</v>
       </c>
       <c r="F99">
-        <v>937.02</v>
+        <v>946.6799999999999</v>
       </c>
       <c r="G99">
         <v>58.5</v>
@@ -9405,37 +9405,37 @@
         <v>119.775</v>
       </c>
       <c r="M99">
-        <v>137.554536</v>
+        <v>138.972624</v>
       </c>
       <c r="N99">
-        <v>-17.77953600000004</v>
+        <v>-19.19762400000002</v>
       </c>
       <c r="O99">
-        <v>-4.267088640000009</v>
+        <v>-4.607429760000004</v>
       </c>
       <c r="P99">
-        <v>-13.51244736000003</v>
+        <v>-14.59019424000001</v>
       </c>
       <c r="Q99">
-        <v>27.58755263999997</v>
+        <v>26.50980575999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.529568166366693</v>
+        <v>2.27145224955004</v>
       </c>
       <c r="T99">
-        <v>20.42462730776868</v>
+        <v>30.63694096165303</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2089789318179954</v>
+        <v>0.2068464937382199</v>
       </c>
       <c r="W99">
-        <v>0.1161218928091183</v>
+        <v>0.1164349347192293</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8707455492416474</v>
+        <v>0.8618603905759165</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1595352810158456</v>
+        <v>0.1605452810158456</v>
       </c>
       <c r="C100">
-        <v>-304.9736887455845</v>
+        <v>-318.1596113879202</v>
       </c>
       <c r="D100">
-        <v>583.2063112544155</v>
+        <v>579.6803886120798</v>
       </c>
       <c r="E100">
-        <v>525.78</v>
+        <v>535.4400000000001</v>
       </c>
       <c r="F100">
-        <v>946.6799999999999</v>
+        <v>956.34</v>
       </c>
       <c r="G100">
         <v>58.5</v>
@@ -9487,37 +9487,37 @@
         <v>119.775</v>
       </c>
       <c r="M100">
-        <v>138.972624</v>
+        <v>140.390712</v>
       </c>
       <c r="N100">
-        <v>-19.19762400000002</v>
+        <v>-20.61571200000003</v>
       </c>
       <c r="O100">
-        <v>-4.607429760000004</v>
+        <v>-4.947770880000007</v>
       </c>
       <c r="P100">
-        <v>-14.59019424000001</v>
+        <v>-15.66794112000002</v>
       </c>
       <c r="Q100">
-        <v>26.50980575999998</v>
+        <v>25.43205887999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.27145224955004</v>
+        <v>4.497104499100081</v>
       </c>
       <c r="T100">
-        <v>30.63694096165303</v>
+        <v>61.27388192330606</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2068464937382199</v>
+        <v>0.2047571352156116</v>
       </c>
       <c r="W100">
-        <v>0.1164349347192293</v>
+        <v>0.1167416525503482</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8618603905759165</v>
+        <v>0.8531547300650486</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1605452810158456</v>
-      </c>
-      <c r="C101">
-        <v>-318.1596113879202</v>
-      </c>
-      <c r="D101">
-        <v>579.6803886120798</v>
-      </c>
-      <c r="E101">
-        <v>535.4400000000001</v>
-      </c>
-      <c r="F101">
-        <v>956.34</v>
-      </c>
-      <c r="G101">
-        <v>58.5</v>
-      </c>
-      <c r="H101">
-        <v>545.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>160.875</v>
-      </c>
-      <c r="K101">
-        <v>41.1</v>
-      </c>
-      <c r="L101">
-        <v>119.775</v>
-      </c>
-      <c r="M101">
-        <v>140.390712</v>
-      </c>
-      <c r="N101">
-        <v>-20.61571200000003</v>
-      </c>
-      <c r="O101">
-        <v>-4.947770880000007</v>
-      </c>
-      <c r="P101">
-        <v>-15.66794112000002</v>
-      </c>
-      <c r="Q101">
-        <v>25.43205887999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.497104499100081</v>
-      </c>
-      <c r="T101">
-        <v>61.27388192330606</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2047571352156116</v>
-      </c>
-      <c r="W101">
-        <v>0.1167416525503482</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8531547300650486</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
